--- a/research/traditional_assets/database/data/jamaica/jamaica_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_office_equipment_services.xlsx
@@ -1397,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1534,22 +1534,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.125269053954939</v>
+        <v>0.1249896313200516</v>
       </c>
       <c r="C2">
-        <v>24.93540731839009</v>
+        <v>24.76520723205104</v>
       </c>
       <c r="D2">
-        <v>22.29540731839009</v>
+        <v>22.37407723205104</v>
       </c>
       <c r="E2">
-        <v>-0.387</v>
+        <v>-0.13813</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.24887</v>
       </c>
       <c r="G2">
         <v>2.64</v>
@@ -1570,28 +1570,28 @@
         <v>1.313</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.012518161</v>
       </c>
       <c r="N2">
-        <v>1.313</v>
+        <v>1.300481839</v>
       </c>
       <c r="O2">
-        <v>0.32825</v>
+        <v>0.32512045975</v>
       </c>
       <c r="P2">
-        <v>0.9847500000000001</v>
+        <v>0.9753613792500001</v>
       </c>
       <c r="Q2">
-        <v>1.24175</v>
+        <v>1.23236137925</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.125269053954939</v>
+        <v>0.1258710922424764</v>
       </c>
       <c r="T2">
-        <v>0.7685264885431575</v>
+        <v>0.7743486589109088</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>104.8876108878932</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1616,22 +1616,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1249896313200516</v>
+        <v>0.1247102086851643</v>
       </c>
       <c r="C3">
-        <v>24.76520723205104</v>
+        <v>24.59556428920274</v>
       </c>
       <c r="D3">
-        <v>22.37407723205104</v>
+        <v>22.45330428920274</v>
       </c>
       <c r="E3">
-        <v>-0.13813</v>
+        <v>0.11074</v>
       </c>
       <c r="F3">
-        <v>0.24887</v>
+        <v>0.49774</v>
       </c>
       <c r="G3">
         <v>2.64</v>
@@ -1652,28 +1652,28 @@
         <v>1.313</v>
       </c>
       <c r="M3">
-        <v>0.012518161</v>
+        <v>0.025036322</v>
       </c>
       <c r="N3">
-        <v>1.300481839</v>
+        <v>1.287963678</v>
       </c>
       <c r="O3">
-        <v>0.32512045975</v>
+        <v>0.3219909195</v>
       </c>
       <c r="P3">
-        <v>0.9753613792500001</v>
+        <v>0.9659727585000001</v>
       </c>
       <c r="Q3">
-        <v>1.23236137925</v>
+        <v>1.2229727585</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1258710922424764</v>
+        <v>0.1264854170256778</v>
       </c>
       <c r="T3">
-        <v>0.7743486589109088</v>
+        <v>0.7802896490820834</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>104.8876108878932</v>
+        <v>52.4438054439466</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1698,22 +1698,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1247102086851643</v>
+        <v>0.1244307860502769</v>
       </c>
       <c r="C4">
-        <v>24.59556428920274</v>
+        <v>24.42648442944635</v>
       </c>
       <c r="D4">
-        <v>22.45330428920274</v>
+        <v>22.53309442944635</v>
       </c>
       <c r="E4">
-        <v>0.11074</v>
+        <v>0.35961</v>
       </c>
       <c r="F4">
-        <v>0.49774</v>
+        <v>0.74661</v>
       </c>
       <c r="G4">
         <v>2.64</v>
@@ -1734,28 +1734,28 @@
         <v>1.313</v>
       </c>
       <c r="M4">
-        <v>0.025036322</v>
+        <v>0.037554483</v>
       </c>
       <c r="N4">
-        <v>1.287963678</v>
+        <v>1.275445517</v>
       </c>
       <c r="O4">
-        <v>0.3219909195</v>
+        <v>0.31886137925</v>
       </c>
       <c r="P4">
-        <v>0.9659727585000001</v>
+        <v>0.9565841377500001</v>
       </c>
       <c r="Q4">
-        <v>1.2229727585</v>
+        <v>1.21358413775</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1264854170256778</v>
+        <v>0.1271124082992545</v>
       </c>
       <c r="T4">
-        <v>0.7802896490820834</v>
+        <v>0.7863531338959626</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>52.4438054439466</v>
+        <v>34.96253696263107</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1780,22 +1780,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1244307860502769</v>
+        <v>0.1241513634153896</v>
       </c>
       <c r="C5">
-        <v>24.42648442944635</v>
+        <v>24.25797367711204</v>
       </c>
       <c r="D5">
-        <v>22.53309442944635</v>
+        <v>22.61345367711204</v>
       </c>
       <c r="E5">
-        <v>0.35961</v>
+        <v>0.60848</v>
       </c>
       <c r="F5">
-        <v>0.74661</v>
+        <v>0.99548</v>
       </c>
       <c r="G5">
         <v>2.64</v>
@@ -1816,28 +1816,28 @@
         <v>1.313</v>
       </c>
       <c r="M5">
-        <v>0.037554483</v>
+        <v>0.050072644</v>
       </c>
       <c r="N5">
-        <v>1.275445517</v>
+        <v>1.262927356</v>
       </c>
       <c r="O5">
-        <v>0.31886137925</v>
+        <v>0.315731839</v>
       </c>
       <c r="P5">
-        <v>0.9565841377500001</v>
+        <v>0.947195517</v>
       </c>
       <c r="Q5">
-        <v>1.21358413775</v>
+        <v>1.204195517</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1271124082992545</v>
+        <v>0.1277524618910308</v>
       </c>
       <c r="T5">
-        <v>0.7863531338959626</v>
+        <v>0.7925429413101313</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>34.96253696263107</v>
+        <v>26.2219027219733</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1862,22 +1862,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1241513634153896</v>
+        <v>0.1238719407805022</v>
       </c>
       <c r="C6">
-        <v>24.25797367711204</v>
+        <v>24.09003814277527</v>
       </c>
       <c r="D6">
-        <v>22.61345367711204</v>
+        <v>22.69438814277527</v>
       </c>
       <c r="E6">
-        <v>0.60848</v>
+        <v>0.8573500000000001</v>
       </c>
       <c r="F6">
-        <v>0.99548</v>
+        <v>1.24435</v>
       </c>
       <c r="G6">
         <v>2.64</v>
@@ -1898,28 +1898,28 @@
         <v>1.313</v>
       </c>
       <c r="M6">
-        <v>0.050072644</v>
+        <v>0.062590805</v>
       </c>
       <c r="N6">
-        <v>1.262927356</v>
+        <v>1.250409195</v>
       </c>
       <c r="O6">
-        <v>0.315731839</v>
+        <v>0.3126022987500001</v>
       </c>
       <c r="P6">
-        <v>0.947195517</v>
+        <v>0.9378068962500001</v>
       </c>
       <c r="Q6">
-        <v>1.204195517</v>
+        <v>1.19480689625</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1277524618910308</v>
+        <v>0.1284059902952655</v>
       </c>
       <c r="T6">
-        <v>0.7925429413101313</v>
+        <v>0.7988630604593349</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>26.2219027219733</v>
+        <v>20.97752217757864</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1944,22 +1944,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1238719407805022</v>
+        <v>0.1235925181456149</v>
       </c>
       <c r="C7">
-        <v>24.09003814277527</v>
+        <v>23.92268402480574</v>
       </c>
       <c r="D7">
-        <v>22.69438814277527</v>
+        <v>22.77590402480574</v>
       </c>
       <c r="E7">
-        <v>0.8573500000000001</v>
+        <v>1.10622</v>
       </c>
       <c r="F7">
-        <v>1.24435</v>
+        <v>1.49322</v>
       </c>
       <c r="G7">
         <v>2.64</v>
@@ -1980,28 +1980,28 @@
         <v>1.313</v>
       </c>
       <c r="M7">
-        <v>0.062590805</v>
+        <v>0.07510896600000001</v>
       </c>
       <c r="N7">
-        <v>1.250409195</v>
+        <v>1.237891034</v>
       </c>
       <c r="O7">
-        <v>0.3126022987500001</v>
+        <v>0.3094727585000001</v>
       </c>
       <c r="P7">
-        <v>0.9378068962500001</v>
+        <v>0.9284182755000001</v>
       </c>
       <c r="Q7">
-        <v>1.19480689625</v>
+        <v>1.1854182755</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1284059902952655</v>
+        <v>0.1290734235591648</v>
       </c>
       <c r="T7">
-        <v>0.7988630604593349</v>
+        <v>0.8053176502287342</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.97752217757864</v>
+        <v>17.48126848131553</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2026,22 +2026,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1235925181456149</v>
+        <v>0.1233130955107275</v>
       </c>
       <c r="C8">
-        <v>23.92268402480574</v>
+        <v>23.75591761094973</v>
       </c>
       <c r="D8">
-        <v>22.77590402480574</v>
+        <v>22.85800761094973</v>
       </c>
       <c r="E8">
-        <v>1.10622</v>
+        <v>1.35509</v>
       </c>
       <c r="F8">
-        <v>1.49322</v>
+        <v>1.74209</v>
       </c>
       <c r="G8">
         <v>2.64</v>
@@ -2062,28 +2062,28 @@
         <v>1.313</v>
       </c>
       <c r="M8">
-        <v>0.075108966</v>
+        <v>0.08762712699999999</v>
       </c>
       <c r="N8">
-        <v>1.237891034</v>
+        <v>1.225372873</v>
       </c>
       <c r="O8">
-        <v>0.3094727585000001</v>
+        <v>0.30634321825</v>
       </c>
       <c r="P8">
-        <v>0.9284182755000001</v>
+        <v>0.9190296547500001</v>
       </c>
       <c r="Q8">
-        <v>1.1854182755</v>
+        <v>1.17602965475</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1290734235591648</v>
+        <v>0.1297552102265887</v>
       </c>
       <c r="T8">
-        <v>0.8053176502287342</v>
+        <v>0.8119110483802712</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.48126848131554</v>
+        <v>14.98394441255618</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2108,22 +2108,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1233130955107275</v>
+        <v>0.1230336728758402</v>
       </c>
       <c r="C9">
-        <v>23.75591761094973</v>
+        <v>23.58974527994696</v>
       </c>
       <c r="D9">
-        <v>22.85800761094973</v>
+        <v>22.94070527994696</v>
       </c>
       <c r="E9">
-        <v>1.35509</v>
+        <v>1.60396</v>
       </c>
       <c r="F9">
-        <v>1.74209</v>
+        <v>1.99096</v>
       </c>
       <c r="G9">
         <v>2.64</v>
@@ -2144,28 +2144,28 @@
         <v>1.313</v>
       </c>
       <c r="M9">
-        <v>0.087627127</v>
+        <v>0.100145288</v>
       </c>
       <c r="N9">
-        <v>1.225372873</v>
+        <v>1.212854712</v>
       </c>
       <c r="O9">
-        <v>0.30634321825</v>
+        <v>0.303213678</v>
       </c>
       <c r="P9">
-        <v>0.9190296547500001</v>
+        <v>0.9096410340000001</v>
       </c>
       <c r="Q9">
-        <v>1.17602965475</v>
+        <v>1.166641034</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1297552102265887</v>
+        <v>0.1304518183433045</v>
       </c>
       <c r="T9">
-        <v>0.8119110483802712</v>
+        <v>0.8186477812742331</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.98394441255617</v>
+        <v>13.11095136098665</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2190,22 +2190,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1230336728758402</v>
+        <v>0.1228555002409528</v>
       </c>
       <c r="C10">
-        <v>23.58974527994696</v>
+        <v>23.39392023965939</v>
       </c>
       <c r="D10">
-        <v>22.94070527994696</v>
+        <v>22.99375023965939</v>
       </c>
       <c r="E10">
-        <v>1.60396</v>
+        <v>1.85283</v>
       </c>
       <c r="F10">
-        <v>1.99096</v>
+        <v>2.23983</v>
       </c>
       <c r="G10">
         <v>2.64</v>
@@ -2226,45 +2226,45 @@
         <v>1.313</v>
       </c>
       <c r="M10">
-        <v>0.100145288</v>
+        <v>0.116023194</v>
       </c>
       <c r="N10">
-        <v>1.212854712</v>
+        <v>1.196976806</v>
       </c>
       <c r="O10">
-        <v>0.303213678</v>
+        <v>0.2992442015</v>
       </c>
       <c r="P10">
-        <v>0.9096410340000001</v>
+        <v>0.8977326045</v>
       </c>
       <c r="Q10">
-        <v>1.166641034</v>
+        <v>1.1547326045</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1304518183433045</v>
+        <v>0.1311637365285196</v>
       </c>
       <c r="T10">
-        <v>0.8186477812742331</v>
+        <v>0.8255325742317983</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.11095136098665</v>
+        <v>11.31670276203567</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2272,22 +2272,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1228555002409528</v>
+        <v>0.1225873276060655</v>
       </c>
       <c r="C11">
-        <v>23.39392023965939</v>
+        <v>23.22535378426697</v>
       </c>
       <c r="D11">
-        <v>22.99375023965939</v>
+        <v>23.07405378426697</v>
       </c>
       <c r="E11">
-        <v>1.85283</v>
+        <v>2.1017</v>
       </c>
       <c r="F11">
-        <v>2.23983</v>
+        <v>2.4887</v>
       </c>
       <c r="G11">
         <v>2.64</v>
@@ -2308,28 +2308,28 @@
         <v>1.313</v>
       </c>
       <c r="M11">
-        <v>0.116023194</v>
+        <v>0.12891466</v>
       </c>
       <c r="N11">
-        <v>1.196976806</v>
+        <v>1.18408534</v>
       </c>
       <c r="O11">
-        <v>0.2992442015</v>
+        <v>0.2960213350000001</v>
       </c>
       <c r="P11">
-        <v>0.8977326045</v>
+        <v>0.8880640050000002</v>
       </c>
       <c r="Q11">
-        <v>1.1547326045</v>
+        <v>1.145064005</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1311637365285196</v>
+        <v>0.1318914751178505</v>
       </c>
       <c r="T11">
-        <v>0.8255325742317983</v>
+        <v>0.8325703625884205</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.31670276203567</v>
+        <v>10.1850324858321</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1225873276060655</v>
+        <v>0.1224594049711782</v>
       </c>
       <c r="C12">
-        <v>23.22535378426697</v>
+        <v>23.01498778464011</v>
       </c>
       <c r="D12">
-        <v>23.07405378426697</v>
+        <v>23.11255778464011</v>
       </c>
       <c r="E12">
-        <v>2.1017</v>
+        <v>2.35057</v>
       </c>
       <c r="F12">
-        <v>2.4887</v>
+        <v>2.73757</v>
       </c>
       <c r="G12">
         <v>2.64</v>
@@ -2390,45 +2390,45 @@
         <v>1.313</v>
       </c>
       <c r="M12">
-        <v>0.12891466</v>
+        <v>0.146459995</v>
       </c>
       <c r="N12">
-        <v>1.18408534</v>
+        <v>1.166540005</v>
       </c>
       <c r="O12">
-        <v>0.2960213350000001</v>
+        <v>0.29163500125</v>
       </c>
       <c r="P12">
-        <v>0.8880640050000002</v>
+        <v>0.8749050037500001</v>
       </c>
       <c r="Q12">
-        <v>1.145064005</v>
+        <v>1.13190500375</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1318914751178505</v>
+        <v>0.1326355673833463</v>
       </c>
       <c r="T12">
-        <v>0.8325703625884205</v>
+        <v>0.8397663034923829</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.1850324858321</v>
+        <v>8.964905399593931</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2436,22 +2436,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1224594049711782</v>
+        <v>0.1222039823362908</v>
       </c>
       <c r="C13">
-        <v>23.01498778464011</v>
+        <v>22.84338431221921</v>
       </c>
       <c r="D13">
-        <v>23.11255778464011</v>
+        <v>23.1898243122192</v>
       </c>
       <c r="E13">
-        <v>2.35057</v>
+        <v>2.59944</v>
       </c>
       <c r="F13">
-        <v>2.73757</v>
+        <v>2.98644</v>
       </c>
       <c r="G13">
         <v>2.64</v>
@@ -2472,28 +2472,28 @@
         <v>1.313</v>
       </c>
       <c r="M13">
-        <v>0.146459995</v>
+        <v>0.15977454</v>
       </c>
       <c r="N13">
-        <v>1.166540005</v>
+        <v>1.15322546</v>
       </c>
       <c r="O13">
-        <v>0.29163500125</v>
+        <v>0.2883063650000001</v>
       </c>
       <c r="P13">
-        <v>0.8749050037500001</v>
+        <v>0.8649190950000002</v>
       </c>
       <c r="Q13">
-        <v>1.13190500375</v>
+        <v>1.121919095</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1326355673833463</v>
+        <v>0.1333965708366941</v>
       </c>
       <c r="T13">
-        <v>0.8397663034923829</v>
+        <v>0.8471257885077986</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.964905399593931</v>
+        <v>8.21782994962777</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2518,22 +2518,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1222039823362908</v>
+        <v>0.1220265597014034</v>
       </c>
       <c r="C14">
-        <v>22.84338431221921</v>
+        <v>22.64849024591169</v>
       </c>
       <c r="D14">
-        <v>23.1898243122192</v>
+        <v>23.24380024591169</v>
       </c>
       <c r="E14">
-        <v>2.59944</v>
+        <v>2.84831</v>
       </c>
       <c r="F14">
-        <v>2.98644</v>
+        <v>3.23531</v>
       </c>
       <c r="G14">
         <v>2.64</v>
@@ -2554,45 +2554,45 @@
         <v>1.313</v>
       </c>
       <c r="M14">
-        <v>0.15977454</v>
+        <v>0.175677333</v>
       </c>
       <c r="N14">
-        <v>1.15322546</v>
+        <v>1.137322667</v>
       </c>
       <c r="O14">
-        <v>0.2883063650000001</v>
+        <v>0.28433066675</v>
       </c>
       <c r="P14">
-        <v>0.8649190950000002</v>
+        <v>0.85299200025</v>
       </c>
       <c r="Q14">
-        <v>1.121919095</v>
+        <v>1.10999200025</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1333965708366941</v>
+        <v>0.1341750686223028</v>
       </c>
       <c r="T14">
-        <v>0.8471257885077986</v>
+        <v>0.8546544570867872</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>8.21782994962777</v>
+        <v>7.473929490949182</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2600,22 +2600,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1220265597014034</v>
+        <v>0.1217771370665161</v>
       </c>
       <c r="C15">
-        <v>22.64849024591169</v>
+        <v>22.47592648915766</v>
       </c>
       <c r="D15">
-        <v>23.24380024591169</v>
+        <v>23.32010648915766</v>
       </c>
       <c r="E15">
-        <v>2.84831</v>
+        <v>3.09718</v>
       </c>
       <c r="F15">
-        <v>3.23531</v>
+        <v>3.48418</v>
       </c>
       <c r="G15">
         <v>2.64</v>
@@ -2636,28 +2636,28 @@
         <v>1.313</v>
       </c>
       <c r="M15">
-        <v>0.175677333</v>
+        <v>0.189190974</v>
       </c>
       <c r="N15">
-        <v>1.137322667</v>
+        <v>1.123809026</v>
       </c>
       <c r="O15">
-        <v>0.28433066675</v>
+        <v>0.2809522565000001</v>
       </c>
       <c r="P15">
-        <v>0.85299200025</v>
+        <v>0.8428567695000002</v>
       </c>
       <c r="Q15">
-        <v>1.10999200025</v>
+        <v>1.0998567695</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1341750686223028</v>
+        <v>0.1349716710075769</v>
       </c>
       <c r="T15">
-        <v>0.8546544570867872</v>
+        <v>0.8623582109815663</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.473929490949182</v>
+        <v>6.940077384452813</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2682,22 +2682,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1217771370665161</v>
+        <v>0.1215277144316287</v>
       </c>
       <c r="C16">
-        <v>22.47592648915766</v>
+        <v>22.30386538864757</v>
       </c>
       <c r="D16">
-        <v>23.32010648915766</v>
+        <v>23.39691538864756</v>
       </c>
       <c r="E16">
-        <v>3.09718</v>
+        <v>3.34605</v>
       </c>
       <c r="F16">
-        <v>3.48418</v>
+        <v>3.73305</v>
       </c>
       <c r="G16">
         <v>2.64</v>
@@ -2718,28 +2718,28 @@
         <v>1.313</v>
       </c>
       <c r="M16">
-        <v>0.189190974</v>
+        <v>0.202704615</v>
       </c>
       <c r="N16">
-        <v>1.123809026</v>
+        <v>1.110295385</v>
       </c>
       <c r="O16">
-        <v>0.2809522565000001</v>
+        <v>0.27757384625</v>
       </c>
       <c r="P16">
-        <v>0.8428567695000002</v>
+        <v>0.8327215387500001</v>
       </c>
       <c r="Q16">
-        <v>1.0998567695</v>
+        <v>1.08972153875</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1349716710075769</v>
+        <v>0.1357870169783868</v>
       </c>
       <c r="T16">
-        <v>0.8623582109815663</v>
+        <v>0.8702432296738696</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.940077384452813</v>
+        <v>6.477405558822625</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2764,22 +2764,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1215277144316287</v>
+        <v>0.1213982917967414</v>
       </c>
       <c r="C17">
-        <v>22.30386538864757</v>
+        <v>22.09505040002238</v>
       </c>
       <c r="D17">
-        <v>23.39691538864756</v>
+        <v>23.43697040002238</v>
       </c>
       <c r="E17">
-        <v>3.34605</v>
+        <v>3.59492</v>
       </c>
       <c r="F17">
-        <v>3.73305</v>
+        <v>3.98192</v>
       </c>
       <c r="G17">
         <v>2.64</v>
@@ -2800,45 +2800,45 @@
         <v>1.313</v>
       </c>
       <c r="M17">
-        <v>0.202704615</v>
+        <v>0.220200176</v>
       </c>
       <c r="N17">
-        <v>1.110295385</v>
+        <v>1.092799824</v>
       </c>
       <c r="O17">
-        <v>0.27757384625</v>
+        <v>0.273199956</v>
       </c>
       <c r="P17">
-        <v>0.8327215387500001</v>
+        <v>0.8195998680000001</v>
       </c>
       <c r="Q17">
-        <v>1.08972153875</v>
+        <v>1.076599868</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1357870169783868</v>
+        <v>0.1366217759485017</v>
       </c>
       <c r="T17">
-        <v>0.8702432296738696</v>
+        <v>0.8783159869064657</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.477405558822626</v>
+        <v>5.962756360376387</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2846,22 +2846,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1213982917967414</v>
+        <v>0.1211563691618541</v>
       </c>
       <c r="C18">
-        <v>22.09505040002238</v>
+        <v>21.92142199799231</v>
       </c>
       <c r="D18">
-        <v>23.43697040002238</v>
+        <v>23.51221199799231</v>
       </c>
       <c r="E18">
-        <v>3.59492</v>
+        <v>3.843790000000001</v>
       </c>
       <c r="F18">
-        <v>3.98192</v>
+        <v>4.230790000000001</v>
       </c>
       <c r="G18">
         <v>2.64</v>
@@ -2882,28 +2882,28 @@
         <v>1.313</v>
       </c>
       <c r="M18">
-        <v>0.220200176</v>
+        <v>0.2339626870000001</v>
       </c>
       <c r="N18">
-        <v>1.092799824</v>
+        <v>1.079037313</v>
       </c>
       <c r="O18">
-        <v>0.273199956</v>
+        <v>0.26975932825</v>
       </c>
       <c r="P18">
-        <v>0.8195998680000001</v>
+        <v>0.8092779847500001</v>
       </c>
       <c r="Q18">
-        <v>1.076599868</v>
+        <v>1.06627798475</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1366217759485017</v>
+        <v>0.1374766495925953</v>
       </c>
       <c r="T18">
-        <v>0.8783159869064657</v>
+        <v>0.886583268409727</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.962756360376387</v>
+        <v>5.6120059862366</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2928,22 +2928,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1211563691618541</v>
+        <v>0.1209144465269667</v>
       </c>
       <c r="C19">
-        <v>21.92142199799231</v>
+        <v>21.74827826027053</v>
       </c>
       <c r="D19">
-        <v>23.51221199799231</v>
+        <v>23.58793826027053</v>
       </c>
       <c r="E19">
-        <v>3.843790000000001</v>
+        <v>4.09266</v>
       </c>
       <c r="F19">
-        <v>4.230790000000001</v>
+        <v>4.479660000000001</v>
       </c>
       <c r="G19">
         <v>2.64</v>
@@ -2964,28 +2964,28 @@
         <v>1.313</v>
       </c>
       <c r="M19">
-        <v>0.2339626870000001</v>
+        <v>0.2477251980000001</v>
       </c>
       <c r="N19">
-        <v>1.079037313</v>
+        <v>1.065274802</v>
       </c>
       <c r="O19">
-        <v>0.26975932825</v>
+        <v>0.2663187005</v>
       </c>
       <c r="P19">
-        <v>0.8092779847500001</v>
+        <v>0.7989561015</v>
       </c>
       <c r="Q19">
-        <v>1.06627798475</v>
+        <v>1.0559561015</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1374766495925953</v>
+        <v>0.138352373813374</v>
       </c>
       <c r="T19">
-        <v>0.886583268409727</v>
+        <v>0.8950521909252627</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.6120059862366</v>
+        <v>5.300227875890122</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3010,22 +3010,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1209144465269667</v>
+        <v>0.1206725238920794</v>
       </c>
       <c r="C20">
-        <v>21.74827826027053</v>
+        <v>21.57562388489285</v>
       </c>
       <c r="D20">
-        <v>23.58793826027053</v>
+        <v>23.66415388489285</v>
       </c>
       <c r="E20">
-        <v>4.09266</v>
+        <v>4.341530000000001</v>
       </c>
       <c r="F20">
-        <v>4.47966</v>
+        <v>4.72853</v>
       </c>
       <c r="G20">
         <v>2.64</v>
@@ -3046,28 +3046,28 @@
         <v>1.313</v>
       </c>
       <c r="M20">
-        <v>0.247725198</v>
+        <v>0.261487709</v>
       </c>
       <c r="N20">
-        <v>1.065274802</v>
+        <v>1.051512291</v>
       </c>
       <c r="O20">
-        <v>0.2663187005000001</v>
+        <v>0.26287807275</v>
       </c>
       <c r="P20">
-        <v>0.7989561015000002</v>
+        <v>0.7886342182500001</v>
       </c>
       <c r="Q20">
-        <v>1.0559561015</v>
+        <v>1.04563421825</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.138352373813374</v>
+        <v>0.139249720854419</v>
       </c>
       <c r="T20">
-        <v>0.8950521909252627</v>
+        <v>0.9037302226387131</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.300227875890124</v>
+        <v>5.021268514001169</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3092,22 +3092,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1206725238920794</v>
+        <v>0.120430601257192</v>
       </c>
       <c r="C21">
-        <v>21.57562388489285</v>
+        <v>21.40346363081174</v>
       </c>
       <c r="D21">
-        <v>23.66415388489285</v>
+        <v>23.74086363081174</v>
       </c>
       <c r="E21">
-        <v>4.341530000000001</v>
+        <v>4.590400000000001</v>
       </c>
       <c r="F21">
-        <v>4.72853</v>
+        <v>4.9774</v>
       </c>
       <c r="G21">
         <v>2.64</v>
@@ -3128,28 +3128,28 @@
         <v>1.313</v>
       </c>
       <c r="M21">
-        <v>0.261487709</v>
+        <v>0.27525022</v>
       </c>
       <c r="N21">
-        <v>1.051512291</v>
+        <v>1.03774978</v>
       </c>
       <c r="O21">
-        <v>0.26287807275</v>
+        <v>0.259437445</v>
       </c>
       <c r="P21">
-        <v>0.7886342182500001</v>
+        <v>0.7783123350000001</v>
       </c>
       <c r="Q21">
-        <v>1.04563421825</v>
+        <v>1.035312335</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.139249720854419</v>
+        <v>0.14016950157149</v>
       </c>
       <c r="T21">
-        <v>0.9037302226387131</v>
+        <v>0.9126252051449996</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.021268514001169</v>
+        <v>4.77020508830111</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3174,22 +3174,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.120430601257192</v>
+        <v>0.1201886786223047</v>
       </c>
       <c r="C22">
-        <v>21.40346363081174</v>
+        <v>21.23180231888682</v>
       </c>
       <c r="D22">
-        <v>23.74086363081174</v>
+        <v>23.81807231888682</v>
       </c>
       <c r="E22">
-        <v>4.590400000000001</v>
+        <v>4.839270000000001</v>
       </c>
       <c r="F22">
-        <v>4.9774</v>
+        <v>5.22627</v>
       </c>
       <c r="G22">
         <v>2.64</v>
@@ -3210,28 +3210,28 @@
         <v>1.313</v>
       </c>
       <c r="M22">
-        <v>0.27525022</v>
+        <v>0.289012731</v>
       </c>
       <c r="N22">
-        <v>1.03774978</v>
+        <v>1.023987269</v>
       </c>
       <c r="O22">
-        <v>0.259437445</v>
+        <v>0.25599681725</v>
       </c>
       <c r="P22">
-        <v>0.7783123350000001</v>
+        <v>0.76799045175</v>
       </c>
       <c r="Q22">
-        <v>1.035312335</v>
+        <v>1.02499045175</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.14016950157149</v>
+        <v>0.141112567876335</v>
       </c>
       <c r="T22">
-        <v>0.9126252051449996</v>
+        <v>0.921745377081825</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.77020508830111</v>
+        <v>4.543052465048676</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3256,22 +3256,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1201886786223047</v>
+        <v>0.1203592559874173</v>
       </c>
       <c r="C23">
-        <v>21.23180231888682</v>
+        <v>20.92844110965448</v>
       </c>
       <c r="D23">
-        <v>23.81807231888682</v>
+        <v>23.76358110965448</v>
       </c>
       <c r="E23">
-        <v>4.839269999999999</v>
+        <v>5.088140000000001</v>
       </c>
       <c r="F23">
-        <v>5.22627</v>
+        <v>5.475140000000001</v>
       </c>
       <c r="G23">
         <v>2.64</v>
@@ -3292,45 +3292,45 @@
         <v>1.313</v>
       </c>
       <c r="M23">
-        <v>0.289012731</v>
+        <v>0.3164630920000001</v>
       </c>
       <c r="N23">
-        <v>1.023987269</v>
+        <v>0.9965369080000002</v>
       </c>
       <c r="O23">
-        <v>0.2559968172500001</v>
+        <v>0.249134227</v>
       </c>
       <c r="P23">
-        <v>0.7679904517500002</v>
+        <v>0.7474026810000001</v>
       </c>
       <c r="Q23">
-        <v>1.02499045175</v>
+        <v>1.004402681</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.141112567876335</v>
+        <v>0.1420798153684837</v>
       </c>
       <c r="T23">
-        <v>0.921745377081825</v>
+        <v>0.9310993995811331</v>
       </c>
       <c r="U23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.543052465048678</v>
+        <v>4.148983035279198</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3338,22 +3338,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1203592559874173</v>
+        <v>0.12073983335253</v>
       </c>
       <c r="C24">
-        <v>20.92844110965448</v>
+        <v>20.55888921486284</v>
       </c>
       <c r="D24">
-        <v>23.76358110965448</v>
+        <v>23.64289921486284</v>
       </c>
       <c r="E24">
-        <v>5.088140000000001</v>
+        <v>5.337010000000001</v>
       </c>
       <c r="F24">
-        <v>5.475140000000001</v>
+        <v>5.724010000000001</v>
       </c>
       <c r="G24">
         <v>2.64</v>
@@ -3374,45 +3374,45 @@
         <v>1.313</v>
       </c>
       <c r="M24">
-        <v>0.3164630920000001</v>
+        <v>0.350881813</v>
       </c>
       <c r="N24">
-        <v>0.9965369080000002</v>
+        <v>0.9621181870000002</v>
       </c>
       <c r="O24">
-        <v>0.249134227</v>
+        <v>0.24052954675</v>
       </c>
       <c r="P24">
-        <v>0.7474026810000001</v>
+        <v>0.7215886402500001</v>
       </c>
       <c r="Q24">
-        <v>1.004402681</v>
+        <v>0.9785886402500001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1420798153684837</v>
+        <v>0.1430721861721168</v>
       </c>
       <c r="T24">
-        <v>0.9310993995811331</v>
+        <v>0.9406963837037999</v>
       </c>
       <c r="U24">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.148983035279198</v>
+        <v>3.742000728889303</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3420,22 +3420,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.12073983335253</v>
+        <v>0.1205429107176426</v>
       </c>
       <c r="C25">
-        <v>20.55888921486284</v>
+        <v>20.37231036682714</v>
       </c>
       <c r="D25">
-        <v>23.64289921486284</v>
+        <v>23.70519036682714</v>
       </c>
       <c r="E25">
-        <v>5.337010000000001</v>
+        <v>5.585880000000001</v>
       </c>
       <c r="F25">
-        <v>5.724010000000001</v>
+        <v>5.972880000000001</v>
       </c>
       <c r="G25">
         <v>2.64</v>
@@ -3456,28 +3456,28 @@
         <v>1.313</v>
       </c>
       <c r="M25">
-        <v>0.350881813</v>
+        <v>0.366137544</v>
       </c>
       <c r="N25">
-        <v>0.9621181870000002</v>
+        <v>0.9468624560000001</v>
       </c>
       <c r="O25">
-        <v>0.24052954675</v>
+        <v>0.236715614</v>
       </c>
       <c r="P25">
-        <v>0.7215886402500001</v>
+        <v>0.7101468420000001</v>
       </c>
       <c r="Q25">
-        <v>0.9785886402500001</v>
+        <v>0.9671468420000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1430721861721168</v>
+        <v>0.1440906719968982</v>
       </c>
       <c r="T25">
-        <v>0.9406963837037999</v>
+        <v>0.9505459200402212</v>
       </c>
       <c r="U25">
         <v>0.0613</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.742000728889303</v>
+        <v>3.586084031852248</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3502,22 +3502,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1205429107176426</v>
+        <v>0.1208709880827553</v>
       </c>
       <c r="C26">
-        <v>20.37231036682714</v>
+        <v>20.01984327035002</v>
       </c>
       <c r="D26">
-        <v>23.70519036682714</v>
+        <v>23.60159327035002</v>
       </c>
       <c r="E26">
-        <v>5.58588</v>
+        <v>5.83475</v>
       </c>
       <c r="F26">
-        <v>5.97288</v>
+        <v>6.22175</v>
       </c>
       <c r="G26">
         <v>2.64</v>
@@ -3538,45 +3538,45 @@
         <v>1.313</v>
       </c>
       <c r="M26">
-        <v>0.366137544</v>
+        <v>0.398814175</v>
       </c>
       <c r="N26">
-        <v>0.9468624560000002</v>
+        <v>0.9141858250000001</v>
       </c>
       <c r="O26">
-        <v>0.236715614</v>
+        <v>0.22854645625</v>
       </c>
       <c r="P26">
-        <v>0.7101468420000001</v>
+        <v>0.6856393687500001</v>
       </c>
       <c r="Q26">
-        <v>0.9671468420000001</v>
+        <v>0.9426393687500001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1440906719968982</v>
+        <v>0.1451363174436737</v>
       </c>
       <c r="T26">
-        <v>0.9505459200402212</v>
+        <v>0.9606581106789469</v>
       </c>
       <c r="U26">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.586084031852249</v>
+        <v>3.292260110864916</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3584,22 +3584,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1208709880827553</v>
+        <v>0.1206950654478679</v>
       </c>
       <c r="C27">
-        <v>20.01984327035002</v>
+        <v>19.82641156192277</v>
       </c>
       <c r="D27">
-        <v>23.60159327035002</v>
+        <v>23.65703156192277</v>
       </c>
       <c r="E27">
-        <v>5.83475</v>
+        <v>6.08362</v>
       </c>
       <c r="F27">
-        <v>6.22175</v>
+        <v>6.47062</v>
       </c>
       <c r="G27">
         <v>2.64</v>
@@ -3620,28 +3620,28 @@
         <v>1.313</v>
       </c>
       <c r="M27">
-        <v>0.398814175</v>
+        <v>0.414766742</v>
       </c>
       <c r="N27">
-        <v>0.9141858250000001</v>
+        <v>0.8982332580000001</v>
       </c>
       <c r="O27">
-        <v>0.22854645625</v>
+        <v>0.2245583145</v>
       </c>
       <c r="P27">
-        <v>0.6856393687500001</v>
+        <v>0.6736749435</v>
       </c>
       <c r="Q27">
-        <v>0.9426393687500001</v>
+        <v>0.9306749435</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1451363174436737</v>
+        <v>0.1462102235781999</v>
       </c>
       <c r="T27">
-        <v>0.9606581106789469</v>
+        <v>0.971043603767368</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.292260110864916</v>
+        <v>3.165634721985496</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3666,22 +3666,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1206950654478679</v>
+        <v>0.1205191428129806</v>
       </c>
       <c r="C28">
-        <v>19.82641156192277</v>
+        <v>19.63324090708795</v>
       </c>
       <c r="D28">
-        <v>23.65703156192277</v>
+        <v>23.71273090708794</v>
       </c>
       <c r="E28">
-        <v>6.08362</v>
+        <v>6.33249</v>
       </c>
       <c r="F28">
-        <v>6.47062</v>
+        <v>6.71949</v>
       </c>
       <c r="G28">
         <v>2.64</v>
@@ -3702,28 +3702,28 @@
         <v>1.313</v>
       </c>
       <c r="M28">
-        <v>0.414766742</v>
+        <v>0.4307193090000001</v>
       </c>
       <c r="N28">
-        <v>0.8982332580000001</v>
+        <v>0.8822806910000001</v>
       </c>
       <c r="O28">
-        <v>0.2245583145</v>
+        <v>0.22057017275</v>
       </c>
       <c r="P28">
-        <v>0.6736749435</v>
+        <v>0.66171051825</v>
       </c>
       <c r="Q28">
-        <v>0.9306749435</v>
+        <v>0.9187105182500001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1462102235781999</v>
+        <v>0.1473135517986036</v>
       </c>
       <c r="T28">
-        <v>0.971043603767368</v>
+        <v>0.9817136309130061</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.165634721985496</v>
+        <v>3.048388991541589</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3748,22 +3748,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1205191428129806</v>
+        <v>0.1219812201780932</v>
       </c>
       <c r="C29">
-        <v>19.63324090708795</v>
+        <v>18.92927387604525</v>
       </c>
       <c r="D29">
-        <v>23.71273090708794</v>
+        <v>23.25763387604525</v>
       </c>
       <c r="E29">
-        <v>6.33249</v>
+        <v>6.58136</v>
       </c>
       <c r="F29">
-        <v>6.71949</v>
+        <v>6.968360000000001</v>
       </c>
       <c r="G29">
         <v>2.64</v>
@@ -3784,45 +3784,45 @@
         <v>1.313</v>
       </c>
       <c r="M29">
-        <v>0.4307193090000001</v>
+        <v>0.5010250840000001</v>
       </c>
       <c r="N29">
-        <v>0.8822806910000001</v>
+        <v>0.811974916</v>
       </c>
       <c r="O29">
-        <v>0.22057017275</v>
+        <v>0.202993729</v>
       </c>
       <c r="P29">
-        <v>0.66171051825</v>
+        <v>0.608981187</v>
       </c>
       <c r="Q29">
-        <v>0.9187105182500001</v>
+        <v>0.865981187</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1473135517986036</v>
+        <v>0.1484475280251295</v>
       </c>
       <c r="T29">
-        <v>0.9817136309130061</v>
+        <v>0.9926800477015786</v>
       </c>
       <c r="U29">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.048388991541589</v>
+        <v>2.62062727382328</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3830,22 +3830,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1219812201780932</v>
+        <v>0.1218637975432059</v>
       </c>
       <c r="C30">
-        <v>18.92927387604525</v>
+        <v>18.71630758765548</v>
       </c>
       <c r="D30">
-        <v>23.25763387604525</v>
+        <v>23.29353758765548</v>
       </c>
       <c r="E30">
-        <v>6.58136</v>
+        <v>6.83023</v>
       </c>
       <c r="F30">
-        <v>6.968360000000001</v>
+        <v>7.217230000000001</v>
       </c>
       <c r="G30">
         <v>2.64</v>
@@ -3866,28 +3866,28 @@
         <v>1.313</v>
       </c>
       <c r="M30">
-        <v>0.5010250840000001</v>
+        <v>0.5189188370000001</v>
       </c>
       <c r="N30">
-        <v>0.811974916</v>
+        <v>0.7940811630000001</v>
       </c>
       <c r="O30">
-        <v>0.202993729</v>
+        <v>0.19852029075</v>
       </c>
       <c r="P30">
-        <v>0.608981187</v>
+        <v>0.5955608722500001</v>
       </c>
       <c r="Q30">
-        <v>0.865981187</v>
+        <v>0.8525608722500001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1484475280251295</v>
+        <v>0.149613447243952</v>
       </c>
       <c r="T30">
-        <v>0.9926800477015786</v>
+        <v>1.003955377639125</v>
       </c>
       <c r="U30">
         <v>0.07190000000000001</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.62062727382328</v>
+        <v>2.530260816105236</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3912,22 +3912,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1218637975432059</v>
+        <v>0.1226238749083185</v>
       </c>
       <c r="C31">
-        <v>18.71630758765548</v>
+        <v>18.23697680062922</v>
       </c>
       <c r="D31">
-        <v>23.29353758765548</v>
+        <v>23.06307680062922</v>
       </c>
       <c r="E31">
-        <v>6.83023</v>
+        <v>7.0791</v>
       </c>
       <c r="F31">
-        <v>7.21723</v>
+        <v>7.4661</v>
       </c>
       <c r="G31">
         <v>2.64</v>
@@ -3948,45 +3948,45 @@
         <v>1.313</v>
       </c>
       <c r="M31">
-        <v>0.5189188370000001</v>
+        <v>0.5659303800000001</v>
       </c>
       <c r="N31">
-        <v>0.7940811630000001</v>
+        <v>0.7470696200000001</v>
       </c>
       <c r="O31">
-        <v>0.19852029075</v>
+        <v>0.186767405</v>
       </c>
       <c r="P31">
-        <v>0.5955608722500001</v>
+        <v>0.5603022150000001</v>
       </c>
       <c r="Q31">
-        <v>0.8525608722500001</v>
+        <v>0.8173022150000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.149613447243952</v>
+        <v>0.1508126784404551</v>
       </c>
       <c r="T31">
-        <v>1.003955377639125</v>
+        <v>1.015552859860601</v>
       </c>
       <c r="U31">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.530260816105236</v>
+        <v>2.320073363087523</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3994,22 +3994,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1226238749083185</v>
+        <v>0.1225357022734312</v>
       </c>
       <c r="C32">
-        <v>18.23697680062922</v>
+        <v>18.01460727159481</v>
       </c>
       <c r="D32">
-        <v>23.06307680062922</v>
+        <v>23.08957727159481</v>
       </c>
       <c r="E32">
-        <v>7.0791</v>
+        <v>7.327970000000001</v>
       </c>
       <c r="F32">
-        <v>7.4661</v>
+        <v>7.71497</v>
       </c>
       <c r="G32">
         <v>2.64</v>
@@ -4030,28 +4030,28 @@
         <v>1.313</v>
       </c>
       <c r="M32">
-        <v>0.5659303800000001</v>
+        <v>0.584794726</v>
       </c>
       <c r="N32">
-        <v>0.7470696200000001</v>
+        <v>0.7282052740000001</v>
       </c>
       <c r="O32">
-        <v>0.186767405</v>
+        <v>0.1820513185</v>
       </c>
       <c r="P32">
-        <v>0.5603022150000001</v>
+        <v>0.5461539555000001</v>
       </c>
       <c r="Q32">
-        <v>0.8173022150000001</v>
+        <v>0.8031539555000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1508126784404551</v>
+        <v>0.1520466699614945</v>
       </c>
       <c r="T32">
-        <v>1.015552859860601</v>
+        <v>1.027486500987048</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.320073363087523</v>
+        <v>2.245232286858894</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4076,22 +4076,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1225357022734312</v>
+        <v>0.1224475296385438</v>
       </c>
       <c r="C33">
-        <v>18.01460727159481</v>
+        <v>17.79229871298858</v>
       </c>
       <c r="D33">
-        <v>23.08957727159481</v>
+        <v>23.11613871298858</v>
       </c>
       <c r="E33">
-        <v>7.327970000000001</v>
+        <v>7.576840000000001</v>
       </c>
       <c r="F33">
-        <v>7.71497</v>
+        <v>7.96384</v>
       </c>
       <c r="G33">
         <v>2.64</v>
@@ -4112,28 +4112,28 @@
         <v>1.313</v>
       </c>
       <c r="M33">
-        <v>0.584794726</v>
+        <v>0.603659072</v>
       </c>
       <c r="N33">
-        <v>0.7282052740000001</v>
+        <v>0.7093409280000001</v>
       </c>
       <c r="O33">
-        <v>0.1820513185</v>
+        <v>0.177335232</v>
       </c>
       <c r="P33">
-        <v>0.5461539555000001</v>
+        <v>0.5320056960000001</v>
       </c>
       <c r="Q33">
-        <v>0.8031539555000001</v>
+        <v>0.7890056960000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1520466699614945</v>
+        <v>0.1533169553507998</v>
       </c>
       <c r="T33">
-        <v>1.027486500987048</v>
+        <v>1.03977113155839</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.245232286858894</v>
+        <v>2.175068777894553</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4158,22 +4158,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1224475296385438</v>
+        <v>0.1223593570036565</v>
       </c>
       <c r="C34">
-        <v>17.79229871298858</v>
+        <v>17.57005133546761</v>
       </c>
       <c r="D34">
-        <v>23.11613871298858</v>
+        <v>23.14276133546761</v>
       </c>
       <c r="E34">
-        <v>7.576840000000001</v>
+        <v>7.825710000000001</v>
       </c>
       <c r="F34">
-        <v>7.96384</v>
+        <v>8.212710000000001</v>
       </c>
       <c r="G34">
         <v>2.64</v>
@@ -4194,28 +4194,28 @@
         <v>1.313</v>
       </c>
       <c r="M34">
-        <v>0.603659072</v>
+        <v>0.6225234180000001</v>
       </c>
       <c r="N34">
-        <v>0.7093409280000001</v>
+        <v>0.6904765820000001</v>
       </c>
       <c r="O34">
-        <v>0.177335232</v>
+        <v>0.1726191455</v>
       </c>
       <c r="P34">
-        <v>0.5320056960000001</v>
+        <v>0.5178574365</v>
       </c>
       <c r="Q34">
-        <v>0.7890056960000001</v>
+        <v>0.7748574365000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1533169553507998</v>
+        <v>0.15462515970695</v>
       </c>
       <c r="T34">
-        <v>1.03977113155839</v>
+        <v>1.052422467519921</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.175068777894553</v>
+        <v>2.109157602806839</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4240,22 +4240,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1223593570036565</v>
+        <v>0.1222711843687691</v>
       </c>
       <c r="C35">
-        <v>17.57005133546761</v>
+        <v>17.34786535066054</v>
       </c>
       <c r="D35">
-        <v>23.14276133546761</v>
+        <v>23.16944535066054</v>
       </c>
       <c r="E35">
-        <v>7.825710000000001</v>
+        <v>8.074580000000001</v>
       </c>
       <c r="F35">
-        <v>8.212710000000001</v>
+        <v>8.461580000000001</v>
       </c>
       <c r="G35">
         <v>2.64</v>
@@ -4276,28 +4276,28 @@
         <v>1.313</v>
       </c>
       <c r="M35">
-        <v>0.6225234180000001</v>
+        <v>0.6413877640000002</v>
       </c>
       <c r="N35">
-        <v>0.6904765820000001</v>
+        <v>0.671612236</v>
       </c>
       <c r="O35">
-        <v>0.1726191455</v>
+        <v>0.167903059</v>
       </c>
       <c r="P35">
-        <v>0.5178574365</v>
+        <v>0.503709177</v>
       </c>
       <c r="Q35">
-        <v>0.7748574365000001</v>
+        <v>0.760709177</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.15462515970695</v>
+        <v>0.1559730066193472</v>
       </c>
       <c r="T35">
-        <v>1.052422467519921</v>
+        <v>1.065457177298468</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.109157602806839</v>
+        <v>2.047123555665461</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4322,22 +4322,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1222711843687691</v>
+        <v>0.1259105117338818</v>
       </c>
       <c r="C36">
-        <v>17.34786535066054</v>
+        <v>16.04643439861911</v>
       </c>
       <c r="D36">
-        <v>23.16944535066054</v>
+        <v>22.11688439861911</v>
       </c>
       <c r="E36">
-        <v>8.074580000000001</v>
+        <v>8.323450000000001</v>
       </c>
       <c r="F36">
-        <v>8.461580000000001</v>
+        <v>8.710450000000002</v>
       </c>
       <c r="G36">
         <v>2.64</v>
@@ -4358,45 +4358,45 @@
         <v>1.313</v>
       </c>
       <c r="M36">
-        <v>0.6413877640000002</v>
+        <v>0.7839405000000002</v>
       </c>
       <c r="N36">
-        <v>0.671612236</v>
+        <v>0.5290595</v>
       </c>
       <c r="O36">
-        <v>0.167903059</v>
+        <v>0.132264875</v>
       </c>
       <c r="P36">
-        <v>0.503709177</v>
+        <v>0.396794625</v>
       </c>
       <c r="Q36">
-        <v>0.760709177</v>
+        <v>0.653794625</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1559730066193472</v>
+        <v>0.1573623257444336</v>
       </c>
       <c r="T36">
-        <v>1.065457177298468</v>
+        <v>1.078892955070202</v>
       </c>
       <c r="U36">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.047123555665461</v>
+        <v>1.674872008781279</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4404,22 +4404,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1259105117338818</v>
+        <v>0.1259288390989945</v>
       </c>
       <c r="C37">
-        <v>16.04643439861911</v>
+        <v>15.79250574283317</v>
       </c>
       <c r="D37">
-        <v>22.11688439861911</v>
+        <v>22.11182574283317</v>
       </c>
       <c r="E37">
-        <v>8.323450000000001</v>
+        <v>8.572320000000001</v>
       </c>
       <c r="F37">
-        <v>8.710450000000002</v>
+        <v>8.959320000000002</v>
       </c>
       <c r="G37">
         <v>2.64</v>
@@ -4440,28 +4440,28 @@
         <v>1.313</v>
       </c>
       <c r="M37">
-        <v>0.7839405000000002</v>
+        <v>0.8063388000000001</v>
       </c>
       <c r="N37">
-        <v>0.5290595</v>
+        <v>0.5066612</v>
       </c>
       <c r="O37">
-        <v>0.132264875</v>
+        <v>0.1266653</v>
       </c>
       <c r="P37">
-        <v>0.396794625</v>
+        <v>0.3799959000000001</v>
       </c>
       <c r="Q37">
-        <v>0.653794625</v>
+        <v>0.6369959000000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1573623257444336</v>
+        <v>0.1587950610921789</v>
       </c>
       <c r="T37">
-        <v>1.078892955070202</v>
+        <v>1.092748600897302</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.674872008781279</v>
+        <v>1.628347786315132</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4486,22 +4486,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1259288390989945</v>
+        <v>0.1259471664641071</v>
       </c>
       <c r="C38">
-        <v>15.79250574283317</v>
+        <v>15.53857940058709</v>
       </c>
       <c r="D38">
-        <v>22.11182574283317</v>
+        <v>22.10676940058709</v>
       </c>
       <c r="E38">
-        <v>8.572319999999999</v>
+        <v>8.82119</v>
       </c>
       <c r="F38">
-        <v>8.95932</v>
+        <v>9.20819</v>
       </c>
       <c r="G38">
         <v>2.64</v>
@@ -4522,28 +4522,28 @@
         <v>1.313</v>
       </c>
       <c r="M38">
-        <v>0.8063387999999999</v>
+        <v>0.8287371</v>
       </c>
       <c r="N38">
-        <v>0.5066612000000003</v>
+        <v>0.4842629000000002</v>
       </c>
       <c r="O38">
-        <v>0.1266653000000001</v>
+        <v>0.121065725</v>
       </c>
       <c r="P38">
-        <v>0.3799959000000002</v>
+        <v>0.3631971750000001</v>
       </c>
       <c r="Q38">
-        <v>0.6369959000000002</v>
+        <v>0.6201971750000002</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1587950610921789</v>
+        <v>0.1602732801017573</v>
       </c>
       <c r="T38">
-        <v>1.092748600897302</v>
+        <v>1.107044108496691</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.628347786315132</v>
+        <v>1.584338386684994</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4568,22 +4568,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1259471664641071</v>
+        <v>0.1259654938292198</v>
       </c>
       <c r="C39">
-        <v>15.53857940058709</v>
+        <v>15.28465537029409</v>
       </c>
       <c r="D39">
-        <v>22.10676940058709</v>
+        <v>22.10171537029409</v>
       </c>
       <c r="E39">
-        <v>8.82119</v>
+        <v>9.07006</v>
       </c>
       <c r="F39">
-        <v>9.20819</v>
+        <v>9.45706</v>
       </c>
       <c r="G39">
         <v>2.64</v>
@@ -4604,28 +4604,28 @@
         <v>1.313</v>
       </c>
       <c r="M39">
-        <v>0.8287371</v>
+        <v>0.8511354</v>
       </c>
       <c r="N39">
-        <v>0.4842629000000002</v>
+        <v>0.4618646000000002</v>
       </c>
       <c r="O39">
-        <v>0.121065725</v>
+        <v>0.11546615</v>
       </c>
       <c r="P39">
-        <v>0.3631971750000001</v>
+        <v>0.3463984500000001</v>
       </c>
       <c r="Q39">
-        <v>0.6201971750000002</v>
+        <v>0.6033984500000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1602732801017573</v>
+        <v>0.1617991835955158</v>
       </c>
       <c r="T39">
-        <v>1.107044108496691</v>
+        <v>1.121800761502512</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.584338386684994</v>
+        <v>1.542645271245915</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4650,22 +4650,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1259654938292198</v>
+        <v>0.1259838211943324</v>
       </c>
       <c r="C40">
-        <v>15.28465537029409</v>
+        <v>15.03073365036888</v>
       </c>
       <c r="D40">
-        <v>22.10171537029409</v>
+        <v>22.09666365036888</v>
       </c>
       <c r="E40">
-        <v>9.07006</v>
+        <v>9.31893</v>
       </c>
       <c r="F40">
-        <v>9.45706</v>
+        <v>9.70593</v>
       </c>
       <c r="G40">
         <v>2.64</v>
@@ -4686,28 +4686,28 @@
         <v>1.313</v>
       </c>
       <c r="M40">
-        <v>0.8511354</v>
+        <v>0.8735337</v>
       </c>
       <c r="N40">
-        <v>0.4618646000000002</v>
+        <v>0.4394663000000002</v>
       </c>
       <c r="O40">
-        <v>0.11546615</v>
+        <v>0.109866575</v>
       </c>
       <c r="P40">
-        <v>0.3463984500000001</v>
+        <v>0.3295997250000001</v>
       </c>
       <c r="Q40">
-        <v>0.6033984500000001</v>
+        <v>0.5865997250000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1617991835955158</v>
+        <v>0.1633751167120203</v>
       </c>
       <c r="T40">
-        <v>1.121800761502512</v>
+        <v>1.137041239197049</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.542645271245915</v>
+        <v>1.503090264290891</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4732,22 +4732,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1259838211943324</v>
+        <v>0.1453393388577655</v>
       </c>
       <c r="C41">
-        <v>15.03073365036888</v>
+        <v>10.48514670915234</v>
       </c>
       <c r="D41">
-        <v>22.09666365036888</v>
+        <v>17.79994670915234</v>
       </c>
       <c r="E41">
-        <v>9.31893</v>
+        <v>9.5678</v>
       </c>
       <c r="F41">
-        <v>9.70593</v>
+        <v>9.954800000000001</v>
       </c>
       <c r="G41">
         <v>2.64</v>
@@ -4768,45 +4768,45 @@
         <v>1.313</v>
       </c>
       <c r="M41">
-        <v>0.8735337</v>
+        <v>1.46136464</v>
       </c>
       <c r="N41">
-        <v>0.4394663000000002</v>
+        <v>-0.14836464</v>
       </c>
       <c r="O41">
-        <v>0.109866575</v>
+        <v>-0.03709116000000001</v>
       </c>
       <c r="P41">
-        <v>0.3295997250000001</v>
+        <v>-0.11127348</v>
       </c>
       <c r="Q41">
-        <v>0.5865997250000001</v>
+        <v>0.14572652</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1633751167120203</v>
+        <v>0.1663482598781968</v>
       </c>
       <c r="T41">
-        <v>1.137041239197049</v>
+        <v>1.165793805934955</v>
       </c>
       <c r="U41">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.25</v>
+        <v>0.2246188192975574</v>
       </c>
       <c r="W41">
-        <v>0.0675</v>
+        <v>0.1138259573271186</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y41">
-        <v>1.503090264290891</v>
+        <v>0.8984752771902296</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4814,22 +4814,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1453393388577655</v>
+        <v>0.1463493388577655</v>
       </c>
       <c r="C42">
-        <v>10.48514670915234</v>
+        <v>10.05747945020989</v>
       </c>
       <c r="D42">
-        <v>17.79994670915234</v>
+        <v>17.6211494502099</v>
       </c>
       <c r="E42">
-        <v>9.5678</v>
+        <v>9.81667</v>
       </c>
       <c r="F42">
-        <v>9.954800000000001</v>
+        <v>10.20367</v>
       </c>
       <c r="G42">
         <v>2.64</v>
@@ -4850,37 +4850,37 @@
         <v>1.313</v>
       </c>
       <c r="M42">
-        <v>1.46136464</v>
+        <v>1.497898756</v>
       </c>
       <c r="N42">
-        <v>-0.14836464</v>
+        <v>-0.1848987560000002</v>
       </c>
       <c r="O42">
-        <v>-0.03709116000000001</v>
+        <v>-0.04622468900000004</v>
       </c>
       <c r="P42">
-        <v>-0.11127348</v>
+        <v>-0.1386740670000001</v>
       </c>
       <c r="Q42">
-        <v>0.14572652</v>
+        <v>0.1183259329999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1663482598781968</v>
+        <v>0.1683914507235899</v>
       </c>
       <c r="T42">
-        <v>1.165793805934955</v>
+        <v>1.1855530229847</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.2246188192975574</v>
+        <v>0.2191403115098121</v>
       </c>
       <c r="W42">
-        <v>0.1138259573271186</v>
+        <v>0.1146302022703596</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8984752771902296</v>
+        <v>0.8765612460392482</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4896,22 +4896,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1463493388577655</v>
+        <v>0.1473593388577655</v>
       </c>
       <c r="C43">
-        <v>10.05747945020989</v>
+        <v>9.633368441900094</v>
       </c>
       <c r="D43">
-        <v>17.6211494502099</v>
+        <v>17.44590844190009</v>
       </c>
       <c r="E43">
-        <v>9.81667</v>
+        <v>10.06554</v>
       </c>
       <c r="F43">
-        <v>10.20367</v>
+        <v>10.45254</v>
       </c>
       <c r="G43">
         <v>2.64</v>
@@ -4932,37 +4932,37 @@
         <v>1.313</v>
       </c>
       <c r="M43">
-        <v>1.497898756</v>
+        <v>1.534432872</v>
       </c>
       <c r="N43">
-        <v>-0.1848987560000002</v>
+        <v>-0.2214328720000001</v>
       </c>
       <c r="O43">
-        <v>-0.04622468900000004</v>
+        <v>-0.05535821800000001</v>
       </c>
       <c r="P43">
-        <v>-0.1386740670000001</v>
+        <v>-0.166074654</v>
       </c>
       <c r="Q43">
-        <v>0.1183259329999999</v>
+        <v>0.09092534599999996</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1683914507235899</v>
+        <v>0.1705050964257208</v>
       </c>
       <c r="T43">
-        <v>1.1855530229847</v>
+        <v>1.205993592346505</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.2191403115098121</v>
+        <v>0.2139226850452927</v>
       </c>
       <c r="W43">
-        <v>0.1146302022703596</v>
+        <v>0.115396149835351</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8765612460392482</v>
+        <v>0.855690740181171</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4978,22 +4978,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1473593388577655</v>
+        <v>0.1483693388577655</v>
       </c>
       <c r="C44">
-        <v>9.633368441900089</v>
+        <v>9.212708629052088</v>
       </c>
       <c r="D44">
-        <v>17.44590844190009</v>
+        <v>17.27411862905209</v>
       </c>
       <c r="E44">
-        <v>10.06554</v>
+        <v>10.31441</v>
       </c>
       <c r="F44">
-        <v>10.45254</v>
+        <v>10.70141</v>
       </c>
       <c r="G44">
         <v>2.64</v>
@@ -5014,37 +5014,37 @@
         <v>1.313</v>
       </c>
       <c r="M44">
-        <v>1.534432872</v>
+        <v>1.570966988</v>
       </c>
       <c r="N44">
-        <v>-0.2214328719999998</v>
+        <v>-0.257966988</v>
       </c>
       <c r="O44">
-        <v>-0.05535821799999996</v>
+        <v>-0.06449174699999999</v>
       </c>
       <c r="P44">
-        <v>-0.1660746539999999</v>
+        <v>-0.193475241</v>
       </c>
       <c r="Q44">
-        <v>0.09092534600000013</v>
+        <v>0.06352475900000004</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1705050964257208</v>
+        <v>0.172692905134944</v>
       </c>
       <c r="T44">
-        <v>1.205993592346505</v>
+        <v>1.227151374668373</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.2139226850452928</v>
+        <v>0.2089477388814487</v>
       </c>
       <c r="W44">
-        <v>0.115396149835351</v>
+        <v>0.1161264719322033</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8556907401811711</v>
+        <v>0.835790955525795</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5060,22 +5060,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1483693388577655</v>
+        <v>0.1493793388577655</v>
       </c>
       <c r="C45">
-        <v>9.212708629052088</v>
+        <v>8.795399054058267</v>
       </c>
       <c r="D45">
-        <v>17.27411862905209</v>
+        <v>17.10567905405827</v>
       </c>
       <c r="E45">
-        <v>10.31441</v>
+        <v>10.56328</v>
       </c>
       <c r="F45">
-        <v>10.70141</v>
+        <v>10.95028</v>
       </c>
       <c r="G45">
         <v>2.64</v>
@@ -5096,37 +5096,37 @@
         <v>1.313</v>
       </c>
       <c r="M45">
-        <v>1.570966988</v>
+        <v>1.607501104</v>
       </c>
       <c r="N45">
-        <v>-0.257966988</v>
+        <v>-0.2945011040000001</v>
       </c>
       <c r="O45">
-        <v>-0.06449174699999999</v>
+        <v>-0.07362527600000002</v>
       </c>
       <c r="P45">
-        <v>-0.193475241</v>
+        <v>-0.2208758280000001</v>
       </c>
       <c r="Q45">
-        <v>0.06352475900000004</v>
+        <v>0.03612417199999995</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.172692905134944</v>
+        <v>0.1749588498694965</v>
       </c>
       <c r="T45">
-        <v>1.227151374668373</v>
+        <v>1.249064792073166</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.2089477388814487</v>
+        <v>0.2041989266341431</v>
       </c>
       <c r="W45">
-        <v>0.1161264719322033</v>
+        <v>0.1168235975701078</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.835790955525795</v>
+        <v>0.8167957065365723</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5142,22 +5142,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1493793388577655</v>
+        <v>0.1766094847417951</v>
       </c>
       <c r="C46">
-        <v>8.795399054058267</v>
+        <v>4.985700594204465</v>
       </c>
       <c r="D46">
-        <v>17.10567905405827</v>
+        <v>13.54485059420447</v>
       </c>
       <c r="E46">
-        <v>10.56328</v>
+        <v>10.81215</v>
       </c>
       <c r="F46">
-        <v>10.95028</v>
+        <v>11.19915</v>
       </c>
       <c r="G46">
         <v>2.64</v>
@@ -5178,45 +5178,45 @@
         <v>1.313</v>
       </c>
       <c r="M46">
-        <v>1.607501104</v>
+        <v>2.24878932</v>
       </c>
       <c r="N46">
-        <v>-0.2945011040000001</v>
+        <v>-0.93578932</v>
       </c>
       <c r="O46">
-        <v>-0.07362527600000002</v>
+        <v>-0.23394733</v>
       </c>
       <c r="P46">
-        <v>-0.2208758280000001</v>
+        <v>-0.70184199</v>
       </c>
       <c r="Q46">
-        <v>0.03612417199999995</v>
+        <v>-0.44484199</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1749588498694965</v>
+        <v>0.1807983669289956</v>
       </c>
       <c r="T46">
-        <v>1.249064792073166</v>
+        <v>1.305537385078607</v>
       </c>
       <c r="U46">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.2041989266341431</v>
+        <v>0.1459674310441851</v>
       </c>
       <c r="W46">
-        <v>0.1168235975701078</v>
+        <v>0.1714897398463276</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.8167957065365723</v>
+        <v>0.5838697241767405</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5224,22 +5224,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1766094847417951</v>
+        <v>0.178159484741795</v>
       </c>
       <c r="C47">
-        <v>4.985700594204465</v>
+        <v>4.578213186000037</v>
       </c>
       <c r="D47">
-        <v>13.54485059420447</v>
+        <v>13.38623318600004</v>
       </c>
       <c r="E47">
-        <v>10.81215</v>
+        <v>11.06102</v>
       </c>
       <c r="F47">
-        <v>11.19915</v>
+        <v>11.44802</v>
       </c>
       <c r="G47">
         <v>2.64</v>
@@ -5260,37 +5260,37 @@
         <v>1.313</v>
       </c>
       <c r="M47">
-        <v>2.24878932</v>
+        <v>2.298762416</v>
       </c>
       <c r="N47">
-        <v>-0.93578932</v>
+        <v>-0.985762416</v>
       </c>
       <c r="O47">
-        <v>-0.23394733</v>
+        <v>-0.246440604</v>
       </c>
       <c r="P47">
-        <v>-0.70184199</v>
+        <v>-0.739321812</v>
       </c>
       <c r="Q47">
-        <v>-0.44484199</v>
+        <v>-0.482321812</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1807983669289956</v>
+        <v>0.18329833668694</v>
       </c>
       <c r="T47">
-        <v>1.305537385078607</v>
+        <v>1.329714003320803</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1459674310441851</v>
+        <v>0.1427942260214855</v>
       </c>
       <c r="W47">
-        <v>0.1714897398463276</v>
+        <v>0.1721269194148857</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5838697241767405</v>
+        <v>0.5711769040859419</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5306,22 +5306,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.178159484741795</v>
+        <v>0.179709484741795</v>
       </c>
       <c r="C48">
-        <v>4.578213186000037</v>
+        <v>4.174397765380226</v>
       </c>
       <c r="D48">
-        <v>13.38623318600004</v>
+        <v>13.23128776538023</v>
       </c>
       <c r="E48">
-        <v>11.06102</v>
+        <v>11.30989</v>
       </c>
       <c r="F48">
-        <v>11.44802</v>
+        <v>11.69689</v>
       </c>
       <c r="G48">
         <v>2.64</v>
@@ -5342,37 +5342,37 @@
         <v>1.313</v>
       </c>
       <c r="M48">
-        <v>2.298762416</v>
+        <v>2.348735512</v>
       </c>
       <c r="N48">
-        <v>-0.985762416</v>
+        <v>-1.035735512</v>
       </c>
       <c r="O48">
-        <v>-0.246440604</v>
+        <v>-0.258933878</v>
       </c>
       <c r="P48">
-        <v>-0.739321812</v>
+        <v>-0.776801634</v>
       </c>
       <c r="Q48">
-        <v>-0.482321812</v>
+        <v>-0.519801634</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.18329833668694</v>
+        <v>0.1858926449263162</v>
       </c>
       <c r="T48">
-        <v>1.329714003320803</v>
+        <v>1.354802946779686</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1427942260214855</v>
+        <v>0.1397560509997517</v>
       </c>
       <c r="W48">
-        <v>0.1721269194148857</v>
+        <v>0.1727369849592499</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5711769040859419</v>
+        <v>0.559024203999007</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5388,22 +5388,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.179709484741795</v>
+        <v>0.181259484741795</v>
       </c>
       <c r="C49">
-        <v>4.174397765380226</v>
+        <v>3.774128281797134</v>
       </c>
       <c r="D49">
-        <v>13.23128776538023</v>
+        <v>13.07988828179714</v>
       </c>
       <c r="E49">
-        <v>11.30989</v>
+        <v>11.55876</v>
       </c>
       <c r="F49">
-        <v>11.69689</v>
+        <v>11.94576</v>
       </c>
       <c r="G49">
         <v>2.64</v>
@@ -5424,37 +5424,37 @@
         <v>1.313</v>
       </c>
       <c r="M49">
-        <v>2.348735512</v>
+        <v>2.398708608000001</v>
       </c>
       <c r="N49">
-        <v>-1.035735512</v>
+        <v>-1.085708608</v>
       </c>
       <c r="O49">
-        <v>-0.258933878</v>
+        <v>-0.2714271520000001</v>
       </c>
       <c r="P49">
-        <v>-0.776801634</v>
+        <v>-0.8142814560000003</v>
       </c>
       <c r="Q49">
-        <v>-0.519801634</v>
+        <v>-0.5572814560000003</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1858926449263162</v>
+        <v>0.1885867342518223</v>
       </c>
       <c r="T49">
-        <v>1.354802946779686</v>
+        <v>1.380856849602372</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1397560509997517</v>
+        <v>0.1368444666039235</v>
       </c>
       <c r="W49">
-        <v>0.1727369849592499</v>
+        <v>0.1733216311059322</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.559024203999007</v>
+        <v>0.5473778664156942</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5470,22 +5470,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.181259484741795</v>
+        <v>0.182809484741795</v>
       </c>
       <c r="C50">
-        <v>3.774128281797136</v>
+        <v>3.377284388785329</v>
       </c>
       <c r="D50">
-        <v>13.07988828179714</v>
+        <v>12.93191438878533</v>
       </c>
       <c r="E50">
-        <v>11.55876</v>
+        <v>11.80763</v>
       </c>
       <c r="F50">
-        <v>11.94576</v>
+        <v>12.19463</v>
       </c>
       <c r="G50">
         <v>2.64</v>
@@ -5506,37 +5506,37 @@
         <v>1.313</v>
       </c>
       <c r="M50">
-        <v>2.398708608</v>
+        <v>2.448681704</v>
       </c>
       <c r="N50">
-        <v>-1.085708608</v>
+        <v>-1.135681704</v>
       </c>
       <c r="O50">
-        <v>-0.271427152</v>
+        <v>-0.283920426</v>
       </c>
       <c r="P50">
-        <v>-0.814281456</v>
+        <v>-0.851761278</v>
       </c>
       <c r="Q50">
-        <v>-0.557281456</v>
+        <v>-0.594761278</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1885867342518223</v>
+        <v>0.1913864741391129</v>
       </c>
       <c r="T50">
-        <v>1.380856849602372</v>
+        <v>1.40793247410438</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1368444666039236</v>
+        <v>0.134051722387517</v>
       </c>
       <c r="W50">
-        <v>0.1733216311059322</v>
+        <v>0.1738824141445866</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5473778664156943</v>
+        <v>0.5362068895500679</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5552,22 +5552,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.182809484741795</v>
+        <v>0.184359484741795</v>
       </c>
       <c r="C51">
-        <v>3.377284388785329</v>
+        <v>2.983751124917323</v>
       </c>
       <c r="D51">
-        <v>12.93191438878533</v>
+        <v>12.78725112491732</v>
       </c>
       <c r="E51">
-        <v>11.80763</v>
+        <v>12.0565</v>
       </c>
       <c r="F51">
-        <v>12.19463</v>
+        <v>12.4435</v>
       </c>
       <c r="G51">
         <v>2.64</v>
@@ -5588,37 +5588,37 @@
         <v>1.313</v>
       </c>
       <c r="M51">
-        <v>2.448681704</v>
+        <v>2.4986548</v>
       </c>
       <c r="N51">
-        <v>-1.135681704</v>
+        <v>-1.1856548</v>
       </c>
       <c r="O51">
-        <v>-0.283920426</v>
+        <v>-0.2964137</v>
       </c>
       <c r="P51">
-        <v>-0.851761278</v>
+        <v>-0.8892411</v>
       </c>
       <c r="Q51">
-        <v>-0.594761278</v>
+        <v>-0.6322411</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1913864741391129</v>
+        <v>0.1942982036218952</v>
       </c>
       <c r="T51">
-        <v>1.40793247410438</v>
+        <v>1.436091123586467</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.134051722387517</v>
+        <v>0.1313706879397666</v>
       </c>
       <c r="W51">
-        <v>0.1738824141445866</v>
+        <v>0.1744207658616949</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5362068895500679</v>
+        <v>0.5254827517590666</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5634,22 +5634,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.184359484741795</v>
+        <v>0.185909484741795</v>
       </c>
       <c r="C52">
-        <v>2.983751124917323</v>
+        <v>2.593418615936233</v>
       </c>
       <c r="D52">
-        <v>12.78725112491732</v>
+        <v>12.64578861593623</v>
       </c>
       <c r="E52">
-        <v>12.0565</v>
+        <v>12.30537</v>
       </c>
       <c r="F52">
-        <v>12.4435</v>
+        <v>12.69237</v>
       </c>
       <c r="G52">
         <v>2.64</v>
@@ -5670,37 +5670,37 @@
         <v>1.313</v>
       </c>
       <c r="M52">
-        <v>2.4986548</v>
+        <v>2.548627896</v>
       </c>
       <c r="N52">
-        <v>-1.1856548</v>
+        <v>-1.235627896</v>
       </c>
       <c r="O52">
-        <v>-0.2964137</v>
+        <v>-0.308906974</v>
       </c>
       <c r="P52">
-        <v>-0.8892411</v>
+        <v>-0.926720922</v>
       </c>
       <c r="Q52">
-        <v>-0.6322411</v>
+        <v>-0.669720922</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1942982036218952</v>
+        <v>0.1973287792060155</v>
       </c>
       <c r="T52">
-        <v>1.436091123586467</v>
+        <v>1.465399105700477</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1313706879397666</v>
+        <v>0.1287947920978104</v>
       </c>
       <c r="W52">
-        <v>0.1744207658616949</v>
+        <v>0.1749380057467597</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5254827517590666</v>
+        <v>0.5151791683912417</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5716,22 +5716,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.185909484741795</v>
+        <v>0.187459484741795</v>
       </c>
       <c r="C53">
-        <v>2.593418615936233</v>
+        <v>2.206181796443502</v>
       </c>
       <c r="D53">
-        <v>12.64578861593623</v>
+        <v>12.5074217964435</v>
       </c>
       <c r="E53">
-        <v>12.30537</v>
+        <v>12.55424</v>
       </c>
       <c r="F53">
-        <v>12.69237</v>
+        <v>12.94124</v>
       </c>
       <c r="G53">
         <v>2.64</v>
@@ -5752,37 +5752,37 @@
         <v>1.313</v>
       </c>
       <c r="M53">
-        <v>2.548627896</v>
+        <v>2.598600992</v>
       </c>
       <c r="N53">
-        <v>-1.235627896</v>
+        <v>-1.285600992</v>
       </c>
       <c r="O53">
-        <v>-0.308906974</v>
+        <v>-0.321400248</v>
       </c>
       <c r="P53">
-        <v>-0.926720922</v>
+        <v>-0.964200744</v>
       </c>
       <c r="Q53">
-        <v>-0.669720922</v>
+        <v>-0.707200744</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1973287792060155</v>
+        <v>0.2004856287728075</v>
       </c>
       <c r="T53">
-        <v>1.465399105700477</v>
+        <v>1.495928253735904</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1287947920978104</v>
+        <v>0.1263179691728525</v>
       </c>
       <c r="W53">
-        <v>0.1749380057467597</v>
+        <v>0.1754353517900912</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5151791683912417</v>
+        <v>0.5052718766914102</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5798,22 +5798,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.187459484741795</v>
+        <v>0.2083342867987912</v>
       </c>
       <c r="C54">
-        <v>2.206181796443502</v>
+        <v>0.3509433225267777</v>
       </c>
       <c r="D54">
-        <v>12.5074217964435</v>
+        <v>10.90105332252678</v>
       </c>
       <c r="E54">
-        <v>12.55424</v>
+        <v>12.80311</v>
       </c>
       <c r="F54">
-        <v>12.94124</v>
+        <v>13.19011</v>
       </c>
       <c r="G54">
         <v>2.64</v>
@@ -5834,45 +5834,45 @@
         <v>1.313</v>
       </c>
       <c r="M54">
-        <v>2.598600992</v>
+        <v>3.110227938</v>
       </c>
       <c r="N54">
-        <v>-1.285600992</v>
+        <v>-1.797227938</v>
       </c>
       <c r="O54">
-        <v>-0.321400248</v>
+        <v>-0.4493069845000001</v>
       </c>
       <c r="P54">
-        <v>-0.964200744</v>
+        <v>-1.3479209535</v>
       </c>
       <c r="Q54">
-        <v>-0.707200744</v>
+        <v>-1.0909209535</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2004856287728075</v>
+        <v>0.2054253273786038</v>
       </c>
       <c r="T54">
-        <v>1.495928253735904</v>
+        <v>1.543698914578636</v>
       </c>
       <c r="U54">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.1263179691728525</v>
+        <v>0.1055388886420581</v>
       </c>
       <c r="W54">
-        <v>0.1754353517900912</v>
+        <v>0.2109139300582027</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.5052718766914102</v>
+        <v>0.4221555545682324</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5880,22 +5880,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2083342867987912</v>
+        <v>0.2102342867987912</v>
       </c>
       <c r="C55">
-        <v>0.3509433225267777</v>
+        <v>-0.02388581723672623</v>
       </c>
       <c r="D55">
-        <v>10.90105332252678</v>
+        <v>10.77509418276327</v>
       </c>
       <c r="E55">
-        <v>12.80311</v>
+        <v>13.05198</v>
       </c>
       <c r="F55">
-        <v>13.19011</v>
+        <v>13.43898</v>
       </c>
       <c r="G55">
         <v>2.64</v>
@@ -5916,37 +5916,37 @@
         <v>1.313</v>
       </c>
       <c r="M55">
-        <v>3.110227938</v>
+        <v>3.168911484</v>
       </c>
       <c r="N55">
-        <v>-1.797227938</v>
+        <v>-1.855911484</v>
       </c>
       <c r="O55">
-        <v>-0.4493069845000001</v>
+        <v>-0.463977871</v>
       </c>
       <c r="P55">
-        <v>-1.3479209535</v>
+        <v>-1.391933613</v>
       </c>
       <c r="Q55">
-        <v>-1.0909209535</v>
+        <v>-1.134933613</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2054253273786038</v>
+        <v>0.2088954431911821</v>
       </c>
       <c r="T55">
-        <v>1.543698914578636</v>
+        <v>1.577257586634693</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1055388886420581</v>
+        <v>0.1035844647783163</v>
       </c>
       <c r="W55">
-        <v>0.2109139300582027</v>
+        <v>0.211374783205273</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4221555545682324</v>
+        <v>0.4143378591132652</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5962,22 +5962,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2102342867987912</v>
+        <v>0.2121342867987912</v>
       </c>
       <c r="C56">
-        <v>-0.02388581723672623</v>
+        <v>-0.3958373498615373</v>
       </c>
       <c r="D56">
-        <v>10.77509418276327</v>
+        <v>10.65201265013846</v>
       </c>
       <c r="E56">
-        <v>13.05198</v>
+        <v>13.30085</v>
       </c>
       <c r="F56">
-        <v>13.43898</v>
+        <v>13.68785</v>
       </c>
       <c r="G56">
         <v>2.64</v>
@@ -5998,37 +5998,37 @@
         <v>1.313</v>
       </c>
       <c r="M56">
-        <v>3.168911484</v>
+        <v>3.22759503</v>
       </c>
       <c r="N56">
-        <v>-1.855911484</v>
+        <v>-1.91459503</v>
       </c>
       <c r="O56">
-        <v>-0.463977871</v>
+        <v>-0.4786487575</v>
       </c>
       <c r="P56">
-        <v>-1.391933613</v>
+        <v>-1.4359462725</v>
       </c>
       <c r="Q56">
-        <v>-1.134933613</v>
+        <v>-1.1789462725</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2088954431911821</v>
+        <v>0.2125197863732084</v>
       </c>
       <c r="T56">
-        <v>1.577257586634693</v>
+        <v>1.612307755226575</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1035844647783163</v>
+        <v>0.101701110873256</v>
       </c>
       <c r="W56">
-        <v>0.211374783205273</v>
+        <v>0.2118188780560863</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4143378591132652</v>
+        <v>0.406804443493024</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6044,22 +6044,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2121342867987912</v>
+        <v>0.2140342867987912</v>
       </c>
       <c r="C57">
-        <v>-0.3958373498615373</v>
+        <v>-0.7650087724809893</v>
       </c>
       <c r="D57">
-        <v>10.65201265013846</v>
+        <v>10.53171122751901</v>
       </c>
       <c r="E57">
-        <v>13.30085</v>
+        <v>13.54972</v>
       </c>
       <c r="F57">
-        <v>13.68785</v>
+        <v>13.93672</v>
       </c>
       <c r="G57">
         <v>2.64</v>
@@ -6080,37 +6080,37 @@
         <v>1.313</v>
       </c>
       <c r="M57">
-        <v>3.22759503</v>
+        <v>3.286278576</v>
       </c>
       <c r="N57">
-        <v>-1.91459503</v>
+        <v>-1.973278576</v>
       </c>
       <c r="O57">
-        <v>-0.4786487575</v>
+        <v>-0.4933196440000001</v>
       </c>
       <c r="P57">
-        <v>-1.4359462725</v>
+        <v>-1.479958932</v>
       </c>
       <c r="Q57">
-        <v>-1.1789462725</v>
+        <v>-1.222958932</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2125197863732084</v>
+        <v>0.2163088724271449</v>
       </c>
       <c r="T57">
-        <v>1.612307755226575</v>
+        <v>1.648951113299906</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.101701110873256</v>
+        <v>0.09988501960766213</v>
       </c>
       <c r="W57">
-        <v>0.2118188780560863</v>
+        <v>0.2122471123765133</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.406804443493024</v>
+        <v>0.3995400784306485</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6126,22 +6126,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2140342867987912</v>
+        <v>0.2159342867987912</v>
       </c>
       <c r="C58">
-        <v>-0.7650087724809893</v>
+        <v>-1.131493226973348</v>
       </c>
       <c r="D58">
-        <v>10.53171122751901</v>
+        <v>10.41409677302665</v>
       </c>
       <c r="E58">
-        <v>13.54972</v>
+        <v>13.79859</v>
       </c>
       <c r="F58">
-        <v>13.93672</v>
+        <v>14.18559</v>
       </c>
       <c r="G58">
         <v>2.64</v>
@@ -6162,37 +6162,37 @@
         <v>1.313</v>
       </c>
       <c r="M58">
-        <v>3.286278576</v>
+        <v>3.344962122000001</v>
       </c>
       <c r="N58">
-        <v>-1.973278576</v>
+        <v>-2.031962122</v>
       </c>
       <c r="O58">
-        <v>-0.4933196440000001</v>
+        <v>-0.5079905305000001</v>
       </c>
       <c r="P58">
-        <v>-1.479958932</v>
+        <v>-1.5239715915</v>
       </c>
       <c r="Q58">
-        <v>-1.222958932</v>
+        <v>-1.2669715915</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2163088724271449</v>
+        <v>0.2202741950417297</v>
       </c>
       <c r="T58">
-        <v>1.648951113299906</v>
+        <v>1.687298813609206</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.09988501960766213</v>
+        <v>0.09813265084261542</v>
       </c>
       <c r="W58">
-        <v>0.2122471123765133</v>
+        <v>0.2126603209313113</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3995400784306485</v>
+        <v>0.3925306033704618</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6208,22 +6208,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2159342867987912</v>
+        <v>0.2178342867987912</v>
       </c>
       <c r="C59">
-        <v>-1.131493226973348</v>
+        <v>-1.495379740465758</v>
       </c>
       <c r="D59">
-        <v>10.41409677302665</v>
+        <v>10.29908025953424</v>
       </c>
       <c r="E59">
-        <v>13.79859</v>
+        <v>14.04746</v>
       </c>
       <c r="F59">
-        <v>14.18559</v>
+        <v>14.43446</v>
       </c>
       <c r="G59">
         <v>2.64</v>
@@ -6244,37 +6244,37 @@
         <v>1.313</v>
       </c>
       <c r="M59">
-        <v>3.344962122000001</v>
+        <v>3.403645668000001</v>
       </c>
       <c r="N59">
-        <v>-2.031962122</v>
+        <v>-2.090645668000001</v>
       </c>
       <c r="O59">
-        <v>-0.5079905305000001</v>
+        <v>-0.5226614170000001</v>
       </c>
       <c r="P59">
-        <v>-1.5239715915</v>
+        <v>-1.567984251</v>
       </c>
       <c r="Q59">
-        <v>-1.2669715915</v>
+        <v>-1.310984251</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2202741950417297</v>
+        <v>0.2244283425427233</v>
       </c>
       <c r="T59">
-        <v>1.687298813609206</v>
+        <v>1.727472594885616</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.09813265084261542</v>
+        <v>0.09644070858670827</v>
       </c>
       <c r="W59">
-        <v>0.2126603209313113</v>
+        <v>0.2130592809152542</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3925306033704618</v>
+        <v>0.385762834346833</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6290,22 +6290,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2178342867987912</v>
+        <v>0.2197342867987912</v>
       </c>
       <c r="C60">
-        <v>-1.495379740465756</v>
+        <v>-1.856753450075074</v>
       </c>
       <c r="D60">
-        <v>10.29908025953424</v>
+        <v>10.18657654992493</v>
       </c>
       <c r="E60">
-        <v>14.04746</v>
+        <v>14.29633</v>
       </c>
       <c r="F60">
-        <v>14.43446</v>
+        <v>14.68333</v>
       </c>
       <c r="G60">
         <v>2.64</v>
@@ -6326,37 +6326,37 @@
         <v>1.313</v>
       </c>
       <c r="M60">
-        <v>3.403645668</v>
+        <v>3.462329214</v>
       </c>
       <c r="N60">
-        <v>-2.090645668</v>
+        <v>-2.149329214</v>
       </c>
       <c r="O60">
-        <v>-0.522661417</v>
+        <v>-0.5373323034999999</v>
       </c>
       <c r="P60">
-        <v>-1.567984251</v>
+        <v>-1.6119969105</v>
       </c>
       <c r="Q60">
-        <v>-1.310984251</v>
+        <v>-1.3549969105</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2244283425427233</v>
+        <v>0.2287851313852286</v>
       </c>
       <c r="T60">
-        <v>1.727472594885616</v>
+        <v>1.769606072809655</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.09644070858670828</v>
+        <v>0.09480612030557764</v>
       </c>
       <c r="W60">
-        <v>0.2130592809152542</v>
+        <v>0.2134447168319448</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3857628343468331</v>
+        <v>0.3792244812223106</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6372,22 +6372,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2197342867987912</v>
+        <v>0.2216342867987912</v>
       </c>
       <c r="C61">
-        <v>-1.856753450075074</v>
+        <v>-2.215695813077886</v>
       </c>
       <c r="D61">
-        <v>10.18657654992493</v>
+        <v>10.07650418692211</v>
       </c>
       <c r="E61">
-        <v>14.29633</v>
+        <v>14.5452</v>
       </c>
       <c r="F61">
-        <v>14.68333</v>
+        <v>14.9322</v>
       </c>
       <c r="G61">
         <v>2.64</v>
@@ -6408,37 +6408,37 @@
         <v>1.313</v>
       </c>
       <c r="M61">
-        <v>3.462329214</v>
+        <v>3.52101276</v>
       </c>
       <c r="N61">
-        <v>-2.149329214</v>
+        <v>-2.20801276</v>
       </c>
       <c r="O61">
-        <v>-0.5373323034999999</v>
+        <v>-0.55200319</v>
       </c>
       <c r="P61">
-        <v>-1.6119969105</v>
+        <v>-1.65600957</v>
       </c>
       <c r="Q61">
-        <v>-1.3549969105</v>
+        <v>-1.39900957</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2287851313852286</v>
+        <v>0.2333597596698594</v>
       </c>
       <c r="T61">
-        <v>1.769606072809655</v>
+        <v>1.813846224629896</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.09480612030557764</v>
+        <v>0.09322601830048467</v>
       </c>
       <c r="W61">
-        <v>0.2134447168319448</v>
+        <v>0.2138173048847457</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3792244812223106</v>
+        <v>0.3729040732019386</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6454,22 +6454,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2216342867987912</v>
+        <v>0.2235342867987912</v>
       </c>
       <c r="C62">
-        <v>-2.215695813077886</v>
+        <v>-2.572284803600102</v>
       </c>
       <c r="D62">
-        <v>10.07650418692211</v>
+        <v>9.968785196399898</v>
       </c>
       <c r="E62">
-        <v>14.5452</v>
+        <v>14.79407</v>
       </c>
       <c r="F62">
-        <v>14.9322</v>
+        <v>15.18107</v>
       </c>
       <c r="G62">
         <v>2.64</v>
@@ -6490,37 +6490,37 @@
         <v>1.313</v>
       </c>
       <c r="M62">
-        <v>3.52101276</v>
+        <v>3.579696306</v>
       </c>
       <c r="N62">
-        <v>-2.20801276</v>
+        <v>-2.266696306</v>
       </c>
       <c r="O62">
-        <v>-0.55200319</v>
+        <v>-0.5666740765</v>
       </c>
       <c r="P62">
-        <v>-1.65600957</v>
+        <v>-1.7000222295</v>
       </c>
       <c r="Q62">
-        <v>-1.39900957</v>
+        <v>-1.4430222295</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2333597596698594</v>
+        <v>0.2381689842767789</v>
       </c>
       <c r="T62">
-        <v>1.813846224629896</v>
+        <v>1.860355102184509</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.09322601830048467</v>
+        <v>0.09169772291850951</v>
       </c>
       <c r="W62">
-        <v>0.2138173048847457</v>
+        <v>0.2141776769358155</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3729040732019386</v>
+        <v>0.366790891674038</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6536,22 +6536,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2235342867987912</v>
+        <v>0.2254342867987912</v>
       </c>
       <c r="C63">
-        <v>-2.572284803600102</v>
+        <v>-2.926595096824167</v>
       </c>
       <c r="D63">
-        <v>9.968785196399898</v>
+        <v>9.863344903175832</v>
       </c>
       <c r="E63">
-        <v>14.79407</v>
+        <v>15.04294</v>
       </c>
       <c r="F63">
-        <v>15.18107</v>
+        <v>15.42994</v>
       </c>
       <c r="G63">
         <v>2.64</v>
@@ -6572,37 +6572,37 @@
         <v>1.313</v>
       </c>
       <c r="M63">
-        <v>3.579696306</v>
+        <v>3.638379852</v>
       </c>
       <c r="N63">
-        <v>-2.266696306</v>
+        <v>-2.325379852</v>
       </c>
       <c r="O63">
-        <v>-0.5666740765</v>
+        <v>-0.581344963</v>
       </c>
       <c r="P63">
-        <v>-1.7000222295</v>
+        <v>-1.744034889</v>
       </c>
       <c r="Q63">
-        <v>-1.4430222295</v>
+        <v>-1.487034889</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2381689842767789</v>
+        <v>0.2432313259682731</v>
       </c>
       <c r="T63">
-        <v>1.860355102184509</v>
+        <v>1.909311815399891</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.09169772291850951</v>
+        <v>0.0902187273875658</v>
       </c>
       <c r="W63">
-        <v>0.2141776769358155</v>
+        <v>0.214526424082012</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.366790891674038</v>
+        <v>0.3608749095502632</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6618,22 +6618,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2254342867987912</v>
+        <v>0.2273342867987912</v>
       </c>
       <c r="C64">
-        <v>-2.926595096824167</v>
+        <v>-3.278698241628407</v>
       </c>
       <c r="D64">
-        <v>9.863344903175832</v>
+        <v>9.760111758371593</v>
       </c>
       <c r="E64">
-        <v>15.04294</v>
+        <v>15.29181</v>
       </c>
       <c r="F64">
-        <v>15.42994</v>
+        <v>15.67881</v>
       </c>
       <c r="G64">
         <v>2.64</v>
@@ -6654,37 +6654,37 @@
         <v>1.313</v>
       </c>
       <c r="M64">
-        <v>3.638379852</v>
+        <v>3.697063398</v>
       </c>
       <c r="N64">
-        <v>-2.325379852</v>
+        <v>-2.384063398</v>
       </c>
       <c r="O64">
-        <v>-0.581344963</v>
+        <v>-0.5960158495</v>
       </c>
       <c r="P64">
-        <v>-1.744034889</v>
+        <v>-1.7880475485</v>
       </c>
       <c r="Q64">
-        <v>-1.487034889</v>
+        <v>-1.5310475485</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2432313259682731</v>
+        <v>0.2485673077511994</v>
       </c>
       <c r="T64">
-        <v>1.909311815399891</v>
+        <v>1.960914837437726</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0902187273875658</v>
+        <v>0.08878668409569969</v>
       </c>
       <c r="W64">
-        <v>0.214526424082012</v>
+        <v>0.214864099890234</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3608749095502632</v>
+        <v>0.3551467363827987</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6700,22 +6700,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2273342867987912</v>
+        <v>0.2292342867987912</v>
       </c>
       <c r="C65">
-        <v>-3.278698241628407</v>
+        <v>-3.628662822497288</v>
       </c>
       <c r="D65">
-        <v>9.760111758371593</v>
+        <v>9.659017177502712</v>
       </c>
       <c r="E65">
-        <v>15.29181</v>
+        <v>15.54068</v>
       </c>
       <c r="F65">
-        <v>15.67881</v>
+        <v>15.92768</v>
       </c>
       <c r="G65">
         <v>2.64</v>
@@ -6736,37 +6736,37 @@
         <v>1.313</v>
       </c>
       <c r="M65">
-        <v>3.697063398</v>
+        <v>3.755746944</v>
       </c>
       <c r="N65">
-        <v>-2.384063398</v>
+        <v>-2.442746944</v>
       </c>
       <c r="O65">
-        <v>-0.5960158495</v>
+        <v>-0.610686736</v>
       </c>
       <c r="P65">
-        <v>-1.7880475485</v>
+        <v>-1.832060208</v>
       </c>
       <c r="Q65">
-        <v>-1.5310475485</v>
+        <v>-1.575060208</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2485673077511994</v>
+        <v>0.2541997329665104</v>
       </c>
       <c r="T65">
-        <v>1.960914837437726</v>
+        <v>2.015384694033218</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08878668409569969</v>
+        <v>0.08739939215670438</v>
       </c>
       <c r="W65">
-        <v>0.214864099890234</v>
+        <v>0.2151912233294491</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3551467363827987</v>
+        <v>0.3495975686268175</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6782,22 +6782,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2292342867987912</v>
+        <v>0.2311342867987912</v>
       </c>
       <c r="C66">
-        <v>-3.628662822497288</v>
+        <v>-3.976554611472469</v>
       </c>
       <c r="D66">
-        <v>9.659017177502712</v>
+        <v>9.559995388527533</v>
       </c>
       <c r="E66">
-        <v>15.54068</v>
+        <v>15.78955</v>
       </c>
       <c r="F66">
-        <v>15.92768</v>
+        <v>16.17655</v>
       </c>
       <c r="G66">
         <v>2.64</v>
@@ -6818,37 +6818,37 @@
         <v>1.313</v>
       </c>
       <c r="M66">
-        <v>3.755746944</v>
+        <v>3.814430490000001</v>
       </c>
       <c r="N66">
-        <v>-2.442746944</v>
+        <v>-2.501430490000001</v>
       </c>
       <c r="O66">
-        <v>-0.610686736</v>
+        <v>-0.6253576225000002</v>
       </c>
       <c r="P66">
-        <v>-1.832060208</v>
+        <v>-1.8760728675</v>
       </c>
       <c r="Q66">
-        <v>-1.575060208</v>
+        <v>-1.6190728675</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2541997329665104</v>
+        <v>0.2601540110512679</v>
       </c>
       <c r="T66">
-        <v>2.015384694033218</v>
+        <v>2.072967113862739</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.08739939215670438</v>
+        <v>0.0860547861235243</v>
       </c>
       <c r="W66">
-        <v>0.2151912233294491</v>
+        <v>0.215508281432073</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3495975686268175</v>
+        <v>0.3442191444940972</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6864,22 +6864,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2311342867987912</v>
+        <v>0.2330342867987912</v>
       </c>
       <c r="C67">
-        <v>-3.976554611472469</v>
+        <v>-4.322436710852122</v>
       </c>
       <c r="D67">
-        <v>9.559995388527533</v>
+        <v>9.46298328914788</v>
       </c>
       <c r="E67">
-        <v>15.78955</v>
+        <v>16.03842</v>
       </c>
       <c r="F67">
-        <v>16.17655</v>
+        <v>16.42542</v>
       </c>
       <c r="G67">
         <v>2.64</v>
@@ -6900,37 +6900,37 @@
         <v>1.313</v>
       </c>
       <c r="M67">
-        <v>3.814430490000001</v>
+        <v>3.873114036000001</v>
       </c>
       <c r="N67">
-        <v>-2.501430490000001</v>
+        <v>-2.560114036000001</v>
       </c>
       <c r="O67">
-        <v>-0.6253576225000002</v>
+        <v>-0.6400285090000002</v>
       </c>
       <c r="P67">
-        <v>-1.8760728675</v>
+        <v>-1.920085527000001</v>
       </c>
       <c r="Q67">
-        <v>-1.6190728675</v>
+        <v>-1.663085527000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2601540110512679</v>
+        <v>0.2664585407880699</v>
       </c>
       <c r="T67">
-        <v>2.072967113862739</v>
+        <v>2.133936734858702</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0860547861235243</v>
+        <v>0.08475092572771331</v>
       </c>
       <c r="W67">
-        <v>0.215508281432073</v>
+        <v>0.2158157317134052</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3442191444940972</v>
+        <v>0.3390037029108532</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6946,22 +6946,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2330342867987912</v>
+        <v>0.2349342867987912</v>
       </c>
       <c r="C68">
-        <v>-4.322436710852122</v>
+        <v>-4.666369687289116</v>
       </c>
       <c r="D68">
-        <v>9.46298328914788</v>
+        <v>9.367920312710886</v>
       </c>
       <c r="E68">
-        <v>16.03842</v>
+        <v>16.28729</v>
       </c>
       <c r="F68">
-        <v>16.42542</v>
+        <v>16.67429</v>
       </c>
       <c r="G68">
         <v>2.64</v>
@@ -6982,37 +6982,37 @@
         <v>1.313</v>
       </c>
       <c r="M68">
-        <v>3.873114036000001</v>
+        <v>3.931797582000001</v>
       </c>
       <c r="N68">
-        <v>-2.560114036000001</v>
+        <v>-2.618797582</v>
       </c>
       <c r="O68">
-        <v>-0.6400285090000002</v>
+        <v>-0.6546993955000001</v>
       </c>
       <c r="P68">
-        <v>-1.920085527000001</v>
+        <v>-1.9640981865</v>
       </c>
       <c r="Q68">
-        <v>-1.663085527000001</v>
+        <v>-1.7070981865</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2664585407880699</v>
+        <v>0.2731451632361933</v>
       </c>
       <c r="T68">
-        <v>2.133936734858702</v>
+        <v>2.198601484399875</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08475092572771331</v>
+        <v>0.08348598653774746</v>
       </c>
       <c r="W68">
-        <v>0.2158157317134052</v>
+        <v>0.2161140043743992</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3390037029108532</v>
+        <v>0.3339439461509898</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7028,22 +7028,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2349342867987912</v>
+        <v>0.2368342867987912</v>
       </c>
       <c r="C69">
-        <v>-4.666369687289116</v>
+        <v>-5.008411697886864</v>
       </c>
       <c r="D69">
-        <v>9.367920312710886</v>
+        <v>9.274748302113139</v>
       </c>
       <c r="E69">
-        <v>16.28729</v>
+        <v>16.53616</v>
       </c>
       <c r="F69">
-        <v>16.67429</v>
+        <v>16.92316</v>
       </c>
       <c r="G69">
         <v>2.64</v>
@@ -7064,37 +7064,37 @@
         <v>1.313</v>
       </c>
       <c r="M69">
-        <v>3.931797582000001</v>
+        <v>3.990481128000001</v>
       </c>
       <c r="N69">
-        <v>-2.618797582</v>
+        <v>-2.677481128000001</v>
       </c>
       <c r="O69">
-        <v>-0.6546993955000001</v>
+        <v>-0.6693702820000001</v>
       </c>
       <c r="P69">
-        <v>-1.9640981865</v>
+        <v>-2.008110846000001</v>
       </c>
       <c r="Q69">
-        <v>-1.7070981865</v>
+        <v>-1.751110846</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2731451632361933</v>
+        <v>0.2802496995873243</v>
       </c>
       <c r="T69">
-        <v>2.198601484399875</v>
+        <v>2.26730778078737</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.08348598653774746</v>
+        <v>0.0822582514416041</v>
       </c>
       <c r="W69">
-        <v>0.2161140043743992</v>
+        <v>0.2164035043100697</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3339439461509898</v>
+        <v>0.3290330057664165</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7110,22 +7110,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2368342867987912</v>
+        <v>0.2387342867987912</v>
       </c>
       <c r="C70">
-        <v>-5.008411697886864</v>
+        <v>-5.348618608844497</v>
       </c>
       <c r="D70">
-        <v>9.274748302113139</v>
+        <v>9.183411391155506</v>
       </c>
       <c r="E70">
-        <v>16.53616</v>
+        <v>16.78503</v>
       </c>
       <c r="F70">
-        <v>16.92316</v>
+        <v>17.17203</v>
       </c>
       <c r="G70">
         <v>2.64</v>
@@ -7146,37 +7146,37 @@
         <v>1.313</v>
       </c>
       <c r="M70">
-        <v>3.990481128000001</v>
+        <v>4.049164674000001</v>
       </c>
       <c r="N70">
-        <v>-2.677481128000001</v>
+        <v>-2.736164674000001</v>
       </c>
       <c r="O70">
-        <v>-0.6693702820000001</v>
+        <v>-0.6840411685000002</v>
       </c>
       <c r="P70">
-        <v>-2.008110846000001</v>
+        <v>-2.0521235055</v>
       </c>
       <c r="Q70">
-        <v>-1.751110846</v>
+        <v>-1.7951235055</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2802496995873243</v>
+        <v>0.2878125931223993</v>
       </c>
       <c r="T70">
-        <v>2.26730778078737</v>
+        <v>2.340446741457931</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0822582514416041</v>
+        <v>0.08106610286998665</v>
       </c>
       <c r="W70">
-        <v>0.2164035043100697</v>
+        <v>0.2166846129432572</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3290330057664165</v>
+        <v>0.3242644114799466</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2387342867987912</v>
+        <v>0.2406342867987912</v>
       </c>
       <c r="C71">
-        <v>-5.348618608844497</v>
+        <v>-5.687044107159915</v>
       </c>
       <c r="D71">
-        <v>9.183411391155506</v>
+        <v>9.093855892840088</v>
       </c>
       <c r="E71">
-        <v>16.78503</v>
+        <v>17.0339</v>
       </c>
       <c r="F71">
-        <v>17.17203</v>
+        <v>17.4209</v>
       </c>
       <c r="G71">
         <v>2.64</v>
@@ -7228,37 +7228,37 @@
         <v>1.313</v>
       </c>
       <c r="M71">
-        <v>4.049164674000001</v>
+        <v>4.107848220000001</v>
       </c>
       <c r="N71">
-        <v>-2.736164674000001</v>
+        <v>-2.794848220000001</v>
       </c>
       <c r="O71">
-        <v>-0.6840411685000002</v>
+        <v>-0.6987120550000002</v>
       </c>
       <c r="P71">
-        <v>-2.0521235055</v>
+        <v>-2.096136165000001</v>
       </c>
       <c r="Q71">
-        <v>-1.7951235055</v>
+        <v>-1.839136165000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2878125931223993</v>
+        <v>0.2958796795598125</v>
       </c>
       <c r="T71">
-        <v>2.340446741457931</v>
+        <v>2.418461632839862</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08106610286998665</v>
+        <v>0.07990801568612969</v>
       </c>
       <c r="W71">
-        <v>0.2166846129432572</v>
+        <v>0.2169576899012106</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3242644114799466</v>
+        <v>0.3196320627445188</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7274,22 +7274,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2406342867987912</v>
+        <v>0.2425342867987912</v>
       </c>
       <c r="C72">
-        <v>-5.687044107159915</v>
+        <v>-6.023739805860151</v>
       </c>
       <c r="D72">
-        <v>9.093855892840088</v>
+        <v>9.006030194139852</v>
       </c>
       <c r="E72">
-        <v>17.0339</v>
+        <v>17.28277</v>
       </c>
       <c r="F72">
-        <v>17.4209</v>
+        <v>17.66977</v>
       </c>
       <c r="G72">
         <v>2.64</v>
@@ -7310,37 +7310,37 @@
         <v>1.313</v>
       </c>
       <c r="M72">
-        <v>4.107848220000001</v>
+        <v>4.166531766000001</v>
       </c>
       <c r="N72">
-        <v>-2.794848220000001</v>
+        <v>-2.853531766000001</v>
       </c>
       <c r="O72">
-        <v>-0.6987120550000002</v>
+        <v>-0.7133829415000003</v>
       </c>
       <c r="P72">
-        <v>-2.096136165000001</v>
+        <v>-2.140148824500001</v>
       </c>
       <c r="Q72">
-        <v>-1.839136165000001</v>
+        <v>-1.883148824500001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2958796795598125</v>
+        <v>0.3045031167860131</v>
       </c>
       <c r="T72">
-        <v>2.418461632839862</v>
+        <v>2.501856861558478</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07990801568612969</v>
+        <v>0.07878255067646589</v>
       </c>
       <c r="W72">
-        <v>0.2169576899012106</v>
+        <v>0.2172230745504894</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3196320627445188</v>
+        <v>0.3151302027058636</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7356,22 +7356,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2425342867987912</v>
+        <v>0.2444342867987912</v>
       </c>
       <c r="C73">
-        <v>-6.023739805860147</v>
+        <v>-6.358755343192275</v>
       </c>
       <c r="D73">
-        <v>9.006030194139852</v>
+        <v>8.919884656807724</v>
       </c>
       <c r="E73">
-        <v>17.28277</v>
+        <v>17.53164</v>
       </c>
       <c r="F73">
-        <v>17.66977</v>
+        <v>17.91864</v>
       </c>
       <c r="G73">
         <v>2.64</v>
@@ -7392,37 +7392,37 @@
         <v>1.313</v>
       </c>
       <c r="M73">
-        <v>4.166531766</v>
+        <v>4.225215312</v>
       </c>
       <c r="N73">
-        <v>-2.853531766</v>
+        <v>-2.912215312</v>
       </c>
       <c r="O73">
-        <v>-0.7133829415</v>
+        <v>-0.7280538280000001</v>
       </c>
       <c r="P73">
-        <v>-2.1401488245</v>
+        <v>-2.184161484</v>
       </c>
       <c r="Q73">
-        <v>-1.8831488245</v>
+        <v>-1.927161484</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3045031167860129</v>
+        <v>0.3137425138140849</v>
       </c>
       <c r="T73">
-        <v>2.501856861558478</v>
+        <v>2.591208892328423</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07878255067646592</v>
+        <v>0.07768834858373722</v>
       </c>
       <c r="W73">
-        <v>0.2172230745504894</v>
+        <v>0.2174810874039548</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3151302027058637</v>
+        <v>0.3107533943349489</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7438,22 +7438,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2444342867987912</v>
+        <v>0.2463342867987912</v>
       </c>
       <c r="C74">
-        <v>-6.358755343192275</v>
+        <v>-6.692138476175559</v>
       </c>
       <c r="D74">
-        <v>8.919884656807724</v>
+        <v>8.83537152382444</v>
       </c>
       <c r="E74">
-        <v>17.53164</v>
+        <v>17.78051</v>
       </c>
       <c r="F74">
-        <v>17.91864</v>
+        <v>18.16751</v>
       </c>
       <c r="G74">
         <v>2.64</v>
@@ -7474,37 +7474,37 @@
         <v>1.313</v>
       </c>
       <c r="M74">
-        <v>4.225215312</v>
+        <v>4.283898858000001</v>
       </c>
       <c r="N74">
-        <v>-2.912215312</v>
+        <v>-2.970898858</v>
       </c>
       <c r="O74">
-        <v>-0.7280538280000001</v>
+        <v>-0.7427247145000001</v>
       </c>
       <c r="P74">
-        <v>-2.184161484</v>
+        <v>-2.2281741435</v>
       </c>
       <c r="Q74">
-        <v>-1.927161484</v>
+        <v>-1.9711741435</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3137425138140849</v>
+        <v>0.3236663106220139</v>
       </c>
       <c r="T74">
-        <v>2.591208892328423</v>
+        <v>2.68717959204429</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07768834858373722</v>
+        <v>0.07662412463053533</v>
       </c>
       <c r="W74">
-        <v>0.2174810874039548</v>
+        <v>0.2177320314121198</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3107533943349489</v>
+        <v>0.3064964985221413</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7520,22 +7520,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2463342867987912</v>
+        <v>0.2482342867987912</v>
       </c>
       <c r="C75">
-        <v>-6.692138476175559</v>
+        <v>-7.023935168885238</v>
       </c>
       <c r="D75">
-        <v>8.83537152382444</v>
+        <v>8.752444831114762</v>
       </c>
       <c r="E75">
-        <v>17.78051</v>
+        <v>18.02938</v>
       </c>
       <c r="F75">
-        <v>18.16751</v>
+        <v>18.41638</v>
       </c>
       <c r="G75">
         <v>2.64</v>
@@ -7556,37 +7556,37 @@
         <v>1.313</v>
       </c>
       <c r="M75">
-        <v>4.283898858000001</v>
+        <v>4.342582404</v>
       </c>
       <c r="N75">
-        <v>-2.970898858</v>
+        <v>-3.029582404</v>
       </c>
       <c r="O75">
-        <v>-0.7427247145000001</v>
+        <v>-0.7573956009999999</v>
       </c>
       <c r="P75">
-        <v>-2.2281741435</v>
+        <v>-2.272186803</v>
       </c>
       <c r="Q75">
-        <v>-1.9711741435</v>
+        <v>-2.015186803</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3236663106220139</v>
+        <v>0.3343534764151683</v>
       </c>
       <c r="T75">
-        <v>2.68717959204429</v>
+        <v>2.790532653276764</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07662412463053533</v>
+        <v>0.07558866348687947</v>
       </c>
       <c r="W75">
-        <v>0.2177320314121198</v>
+        <v>0.2179761931497938</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3064964985221413</v>
+        <v>0.3023546539475178</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7602,22 +7602,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2482342867987912</v>
+        <v>0.2501342867987912</v>
       </c>
       <c r="C76">
-        <v>-7.023935168885238</v>
+        <v>-7.354189675810863</v>
       </c>
       <c r="D76">
-        <v>8.752444831114762</v>
+        <v>8.671060324189137</v>
       </c>
       <c r="E76">
-        <v>18.02938</v>
+        <v>18.27825</v>
       </c>
       <c r="F76">
-        <v>18.41638</v>
+        <v>18.66525</v>
       </c>
       <c r="G76">
         <v>2.64</v>
@@ -7638,37 +7638,37 @@
         <v>1.313</v>
       </c>
       <c r="M76">
-        <v>4.342582404</v>
+        <v>4.40126595</v>
       </c>
       <c r="N76">
-        <v>-3.029582404</v>
+        <v>-3.08826595</v>
       </c>
       <c r="O76">
-        <v>-0.7573956009999999</v>
+        <v>-0.7720664875</v>
       </c>
       <c r="P76">
-        <v>-2.272186803</v>
+        <v>-2.3161994625</v>
       </c>
       <c r="Q76">
-        <v>-2.015186803</v>
+        <v>-2.0591994625</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3343534764151683</v>
+        <v>0.3458956154717751</v>
       </c>
       <c r="T76">
-        <v>2.790532653276764</v>
+        <v>2.902153959407834</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07558866348687947</v>
+        <v>0.07458081464038774</v>
       </c>
       <c r="W76">
-        <v>0.2179761931497938</v>
+        <v>0.2182138439077966</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3023546539475178</v>
+        <v>0.298323258561551</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7684,22 +7684,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2501342867987912</v>
+        <v>0.2520342867987912</v>
       </c>
       <c r="C77">
-        <v>-7.354189675810863</v>
+        <v>-7.68294462060684</v>
       </c>
       <c r="D77">
-        <v>8.671060324189137</v>
+        <v>8.59117537939316</v>
       </c>
       <c r="E77">
-        <v>18.27825</v>
+        <v>18.52712</v>
       </c>
       <c r="F77">
-        <v>18.66525</v>
+        <v>18.91412</v>
       </c>
       <c r="G77">
         <v>2.64</v>
@@ -7720,37 +7720,37 @@
         <v>1.313</v>
       </c>
       <c r="M77">
-        <v>4.40126595</v>
+        <v>4.459949496</v>
       </c>
       <c r="N77">
-        <v>-3.08826595</v>
+        <v>-3.146949496</v>
       </c>
       <c r="O77">
-        <v>-0.7720664875</v>
+        <v>-0.786737374</v>
       </c>
       <c r="P77">
-        <v>-2.3161994625</v>
+        <v>-2.360212122</v>
       </c>
       <c r="Q77">
-        <v>-2.0591994625</v>
+        <v>-2.103212122</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3458956154717751</v>
+        <v>0.3583995994497657</v>
       </c>
       <c r="T77">
-        <v>2.902153959407834</v>
+        <v>3.023077041049828</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07458081464038774</v>
+        <v>0.07359948813196159</v>
       </c>
       <c r="W77">
-        <v>0.2182138439077966</v>
+        <v>0.2184452406984835</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.298323258561551</v>
+        <v>0.2943979525278463</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7766,22 +7766,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2520342867987912</v>
+        <v>0.2539342867987912</v>
       </c>
       <c r="C78">
-        <v>-7.68294462060684</v>
+        <v>-8.010241070529659</v>
       </c>
       <c r="D78">
-        <v>8.59117537939316</v>
+        <v>8.512748929470341</v>
       </c>
       <c r="E78">
-        <v>18.52712</v>
+        <v>18.77599</v>
       </c>
       <c r="F78">
-        <v>18.91412</v>
+        <v>19.16299</v>
       </c>
       <c r="G78">
         <v>2.64</v>
@@ -7802,37 +7802,37 @@
         <v>1.313</v>
       </c>
       <c r="M78">
-        <v>4.459949496</v>
+        <v>4.518633042</v>
       </c>
       <c r="N78">
-        <v>-3.146949496</v>
+        <v>-3.205633042</v>
       </c>
       <c r="O78">
-        <v>-0.786737374</v>
+        <v>-0.8014082605</v>
       </c>
       <c r="P78">
-        <v>-2.360212122</v>
+        <v>-2.4042247815</v>
       </c>
       <c r="Q78">
-        <v>-2.103212122</v>
+        <v>-2.1472247815</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3583995994497657</v>
+        <v>0.3719908863823642</v>
       </c>
       <c r="T78">
-        <v>3.023077041049828</v>
+        <v>3.154515173269385</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07359948813196159</v>
+        <v>0.07264365062375429</v>
       </c>
       <c r="W78">
-        <v>0.2184452406984835</v>
+        <v>0.2186706271829187</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2943979525278463</v>
+        <v>0.2905746024950171</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7848,22 +7848,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2539342867987912</v>
+        <v>0.2558342867987912</v>
       </c>
       <c r="C79">
-        <v>-8.010241070529659</v>
+        <v>-8.336118606834853</v>
       </c>
       <c r="D79">
-        <v>8.512748929470341</v>
+        <v>8.435741393165147</v>
       </c>
       <c r="E79">
-        <v>18.77599</v>
+        <v>19.02486</v>
       </c>
       <c r="F79">
-        <v>19.16299</v>
+        <v>19.41186</v>
       </c>
       <c r="G79">
         <v>2.64</v>
@@ -7884,37 +7884,37 @@
         <v>1.313</v>
       </c>
       <c r="M79">
-        <v>4.518633042</v>
+        <v>4.577316588</v>
       </c>
       <c r="N79">
-        <v>-3.205633042</v>
+        <v>-3.264316588</v>
       </c>
       <c r="O79">
-        <v>-0.8014082605</v>
+        <v>-0.8160791470000001</v>
       </c>
       <c r="P79">
-        <v>-2.4042247815</v>
+        <v>-2.448237441</v>
       </c>
       <c r="Q79">
-        <v>-2.1472247815</v>
+        <v>-2.191237441</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3719908863823642</v>
+        <v>0.3868177448542899</v>
       </c>
       <c r="T79">
-        <v>3.154515173269385</v>
+        <v>3.297902226599812</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07264365062375429</v>
+        <v>0.07171232176960358</v>
       </c>
       <c r="W79">
-        <v>0.2186706271829187</v>
+        <v>0.2188902345267275</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2905746024950171</v>
+        <v>0.2868492870784144</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7930,22 +7930,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2558342867987912</v>
+        <v>0.2577342867987912</v>
       </c>
       <c r="C80">
-        <v>-8.336118606834853</v>
+        <v>-8.660615391387323</v>
       </c>
       <c r="D80">
-        <v>8.435741393165147</v>
+        <v>8.360114608612678</v>
       </c>
       <c r="E80">
-        <v>19.02486</v>
+        <v>19.27373</v>
       </c>
       <c r="F80">
-        <v>19.41186</v>
+        <v>19.66073</v>
       </c>
       <c r="G80">
         <v>2.64</v>
@@ -7966,37 +7966,37 @@
         <v>1.313</v>
       </c>
       <c r="M80">
-        <v>4.577316588</v>
+        <v>4.636000134000001</v>
       </c>
       <c r="N80">
-        <v>-3.264316588</v>
+        <v>-3.323000134</v>
       </c>
       <c r="O80">
-        <v>-0.8160791470000001</v>
+        <v>-0.8307500335000001</v>
       </c>
       <c r="P80">
-        <v>-2.448237441</v>
+        <v>-2.4922501005</v>
       </c>
       <c r="Q80">
-        <v>-2.191237441</v>
+        <v>-2.2352501005</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3868177448542899</v>
+        <v>0.4030566850854466</v>
       </c>
       <c r="T80">
-        <v>3.297902226599812</v>
+        <v>3.454945189771232</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07171232176960358</v>
+        <v>0.07080457086112758</v>
       </c>
       <c r="W80">
-        <v>0.2188902345267275</v>
+        <v>0.2191042821909461</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2868492870784144</v>
+        <v>0.2832182834445104</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8012,22 +8012,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2577342867987912</v>
+        <v>0.2596342867987912</v>
       </c>
       <c r="C81">
-        <v>-8.660615391387323</v>
+        <v>-8.983768229720496</v>
       </c>
       <c r="D81">
-        <v>8.360114608612678</v>
+        <v>8.285831770279504</v>
       </c>
       <c r="E81">
-        <v>19.27373</v>
+        <v>19.5226</v>
       </c>
       <c r="F81">
-        <v>19.66073</v>
+        <v>19.9096</v>
       </c>
       <c r="G81">
         <v>2.64</v>
@@ -8048,37 +8048,37 @@
         <v>1.313</v>
       </c>
       <c r="M81">
-        <v>4.636000134000001</v>
+        <v>4.694683680000001</v>
       </c>
       <c r="N81">
-        <v>-3.323000134</v>
+        <v>-3.381683680000001</v>
       </c>
       <c r="O81">
-        <v>-0.8307500335000001</v>
+        <v>-0.8454209200000001</v>
       </c>
       <c r="P81">
-        <v>-2.4922501005</v>
+        <v>-2.536262760000001</v>
       </c>
       <c r="Q81">
-        <v>-2.2352501005</v>
+        <v>-2.27926276</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4030566850854466</v>
+        <v>0.4209195193397189</v>
       </c>
       <c r="T81">
-        <v>3.454945189771232</v>
+        <v>3.627692449259794</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07080457086112758</v>
+        <v>0.06991951372536349</v>
       </c>
       <c r="W81">
-        <v>0.2191042821909461</v>
+        <v>0.2193129786635593</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2832182834445104</v>
+        <v>0.2796780549014539</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8094,22 +8094,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2596342867987912</v>
+        <v>0.2615342867987912</v>
       </c>
       <c r="C82">
-        <v>-8.983768229720496</v>
+        <v>-9.305612630763269</v>
       </c>
       <c r="D82">
-        <v>8.285831770279504</v>
+        <v>8.212857369236731</v>
       </c>
       <c r="E82">
-        <v>19.5226</v>
+        <v>19.77147</v>
       </c>
       <c r="F82">
-        <v>19.9096</v>
+        <v>20.15847</v>
       </c>
       <c r="G82">
         <v>2.64</v>
@@ -8130,37 +8130,37 @@
         <v>1.313</v>
       </c>
       <c r="M82">
-        <v>4.694683680000001</v>
+        <v>4.753367226000001</v>
       </c>
       <c r="N82">
-        <v>-3.381683680000001</v>
+        <v>-3.440367226000001</v>
       </c>
       <c r="O82">
-        <v>-0.8454209200000001</v>
+        <v>-0.8600918065000002</v>
       </c>
       <c r="P82">
-        <v>-2.536262760000001</v>
+        <v>-2.5802754195</v>
       </c>
       <c r="Q82">
-        <v>-2.27926276</v>
+        <v>-2.3232754195</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4209195193397189</v>
+        <v>0.4406626519365462</v>
       </c>
       <c r="T82">
-        <v>3.627692449259794</v>
+        <v>3.818623630799783</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06991951372536349</v>
+        <v>0.06905630985221085</v>
       </c>
       <c r="W82">
-        <v>0.2193129786635593</v>
+        <v>0.2195165221368487</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2796780549014539</v>
+        <v>0.2762252394088435</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8176,22 +8176,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2615342867987912</v>
+        <v>0.2634342867987912</v>
       </c>
       <c r="C83">
-        <v>-9.305612630763269</v>
+        <v>-9.626182863438355</v>
       </c>
       <c r="D83">
-        <v>8.212857369236731</v>
+        <v>8.141157136561645</v>
       </c>
       <c r="E83">
-        <v>19.77147</v>
+        <v>20.02034</v>
       </c>
       <c r="F83">
-        <v>20.15847</v>
+        <v>20.40734</v>
       </c>
       <c r="G83">
         <v>2.64</v>
@@ -8212,37 +8212,37 @@
         <v>1.313</v>
       </c>
       <c r="M83">
-        <v>4.753367226000001</v>
+        <v>4.812050772</v>
       </c>
       <c r="N83">
-        <v>-3.440367226000001</v>
+        <v>-3.499050772</v>
       </c>
       <c r="O83">
-        <v>-0.8600918065000002</v>
+        <v>-0.874762693</v>
       </c>
       <c r="P83">
-        <v>-2.5802754195</v>
+        <v>-2.624288079</v>
       </c>
       <c r="Q83">
-        <v>-2.3232754195</v>
+        <v>-2.367288079</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4406626519365462</v>
+        <v>0.462599465933021</v>
       </c>
       <c r="T83">
-        <v>3.818623630799783</v>
+        <v>4.030769388066438</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06905630985221085</v>
+        <v>0.06821415973206195</v>
       </c>
       <c r="W83">
-        <v>0.2195165221368487</v>
+        <v>0.2197151011351798</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2762252394088435</v>
+        <v>0.2728566389282479</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8258,22 +8258,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2634342867987912</v>
+        <v>0.2653342867987912</v>
       </c>
       <c r="C84">
-        <v>-9.626182863438355</v>
+        <v>-9.945512010321615</v>
       </c>
       <c r="D84">
-        <v>8.141157136561645</v>
+        <v>8.070697989678386</v>
       </c>
       <c r="E84">
-        <v>20.02034</v>
+        <v>20.26921</v>
       </c>
       <c r="F84">
-        <v>20.40734</v>
+        <v>20.65621</v>
       </c>
       <c r="G84">
         <v>2.64</v>
@@ -8294,37 +8294,37 @@
         <v>1.313</v>
       </c>
       <c r="M84">
-        <v>4.812050772</v>
+        <v>4.870734318</v>
       </c>
       <c r="N84">
-        <v>-3.499050772</v>
+        <v>-3.557734318</v>
       </c>
       <c r="O84">
-        <v>-0.874762693</v>
+        <v>-0.8894335795</v>
       </c>
       <c r="P84">
-        <v>-2.624288079</v>
+        <v>-2.6683007385</v>
       </c>
       <c r="Q84">
-        <v>-2.367288079</v>
+        <v>-2.4113007385</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.462599465933021</v>
+        <v>0.48711708157614</v>
       </c>
       <c r="T84">
-        <v>4.030769388066438</v>
+        <v>4.267873469717405</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06821415973206195</v>
+        <v>0.06739230238589253</v>
       </c>
       <c r="W84">
-        <v>0.2197151011351798</v>
+        <v>0.2199088950974065</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2728566389282479</v>
+        <v>0.2695692095435701</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8340,22 +8340,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2653342867987912</v>
+        <v>0.2672342867987912</v>
       </c>
       <c r="C85">
-        <v>-9.945512010321615</v>
+        <v>-10.26363201853883</v>
       </c>
       <c r="D85">
-        <v>8.070697989678386</v>
+        <v>8.001447981461174</v>
       </c>
       <c r="E85">
-        <v>20.26921</v>
+        <v>20.51808</v>
       </c>
       <c r="F85">
-        <v>20.65621</v>
+        <v>20.90508</v>
       </c>
       <c r="G85">
         <v>2.64</v>
@@ -8376,37 +8376,37 @@
         <v>1.313</v>
       </c>
       <c r="M85">
-        <v>4.870734318</v>
+        <v>4.929417864</v>
       </c>
       <c r="N85">
-        <v>-3.557734318</v>
+        <v>-3.616417864</v>
       </c>
       <c r="O85">
-        <v>-0.8894335795</v>
+        <v>-0.9041044660000001</v>
       </c>
       <c r="P85">
-        <v>-2.6683007385</v>
+        <v>-2.712313398</v>
       </c>
       <c r="Q85">
-        <v>-2.4113007385</v>
+        <v>-2.455313398</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.48711708157614</v>
+        <v>0.5146993991746488</v>
       </c>
       <c r="T85">
-        <v>4.267873469717405</v>
+        <v>4.534615561574744</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06739230238589253</v>
+        <v>0.06659001307177476</v>
       </c>
       <c r="W85">
-        <v>0.2199088950974065</v>
+        <v>0.2200980749176755</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2695692095435701</v>
+        <v>0.266360052287099</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8422,22 +8422,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2672342867987911</v>
+        <v>0.2691342867987912</v>
       </c>
       <c r="C86">
-        <v>-10.26363201853882</v>
+        <v>-10.5805737480645</v>
       </c>
       <c r="D86">
-        <v>8.001447981461178</v>
+        <v>7.933376251935504</v>
       </c>
       <c r="E86">
-        <v>20.51808</v>
+        <v>20.76695</v>
       </c>
       <c r="F86">
-        <v>20.90508</v>
+        <v>21.15395</v>
       </c>
       <c r="G86">
         <v>2.64</v>
@@ -8458,37 +8458,37 @@
         <v>1.313</v>
       </c>
       <c r="M86">
-        <v>4.929417863999999</v>
+        <v>4.98810141</v>
       </c>
       <c r="N86">
-        <v>-3.616417863999999</v>
+        <v>-3.675101409999999</v>
       </c>
       <c r="O86">
-        <v>-0.9041044659999998</v>
+        <v>-0.9187753524999999</v>
       </c>
       <c r="P86">
-        <v>-2.712313398</v>
+        <v>-2.756326057499999</v>
       </c>
       <c r="Q86">
-        <v>-2.455313397999999</v>
+        <v>-2.499326057499999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5146993991746484</v>
+        <v>0.545959359119625</v>
       </c>
       <c r="T86">
-        <v>4.53461556157474</v>
+        <v>4.836923265679723</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06659001307177477</v>
+        <v>0.06580660115328331</v>
       </c>
       <c r="W86">
-        <v>0.2200980749176755</v>
+        <v>0.2202828034480558</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2663600522870991</v>
+        <v>0.2632264046131332</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8504,22 +8504,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2691342867987912</v>
+        <v>0.2710342867987912</v>
       </c>
       <c r="C87">
-        <v>-10.5805737480645</v>
+        <v>-10.89636701757605</v>
       </c>
       <c r="D87">
-        <v>7.933376251935504</v>
+        <v>7.866452982423951</v>
       </c>
       <c r="E87">
-        <v>20.76695</v>
+        <v>21.01582</v>
       </c>
       <c r="F87">
-        <v>21.15395</v>
+        <v>21.40282</v>
       </c>
       <c r="G87">
         <v>2.64</v>
@@ -8540,37 +8540,37 @@
         <v>1.313</v>
       </c>
       <c r="M87">
-        <v>4.98810141</v>
+        <v>5.046784956</v>
       </c>
       <c r="N87">
-        <v>-3.675101409999999</v>
+        <v>-3.733784956</v>
       </c>
       <c r="O87">
-        <v>-0.9187753524999999</v>
+        <v>-0.9334462389999999</v>
       </c>
       <c r="P87">
-        <v>-2.756326057499999</v>
+        <v>-2.800338717</v>
       </c>
       <c r="Q87">
-        <v>-2.499326057499999</v>
+        <v>-2.543338717</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.545959359119625</v>
+        <v>0.5816850276281696</v>
       </c>
       <c r="T87">
-        <v>4.836923265679723</v>
+        <v>5.182417784656846</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06580660115328331</v>
+        <v>0.06504140811661721</v>
       </c>
       <c r="W87">
-        <v>0.2202828034480558</v>
+        <v>0.2204632359661017</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2632264046131332</v>
+        <v>0.2601656324664688</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8586,22 +8586,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2710342867987912</v>
+        <v>0.2729342867987912</v>
       </c>
       <c r="C88">
-        <v>-10.89636701757605</v>
+        <v>-11.21104064800656</v>
       </c>
       <c r="D88">
-        <v>7.866452982423951</v>
+        <v>7.800649351993441</v>
       </c>
       <c r="E88">
-        <v>21.01582</v>
+        <v>21.26469</v>
       </c>
       <c r="F88">
-        <v>21.40282</v>
+        <v>21.65169</v>
       </c>
       <c r="G88">
         <v>2.64</v>
@@ -8622,37 +8622,37 @@
         <v>1.313</v>
       </c>
       <c r="M88">
-        <v>5.046784956</v>
+        <v>5.105468502</v>
       </c>
       <c r="N88">
-        <v>-3.733784956</v>
+        <v>-3.792468502</v>
       </c>
       <c r="O88">
-        <v>-0.9334462389999999</v>
+        <v>-0.9481171254999999</v>
       </c>
       <c r="P88">
-        <v>-2.800338717</v>
+        <v>-2.8443513765</v>
       </c>
       <c r="Q88">
-        <v>-2.543338717</v>
+        <v>-2.5873513765</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5816850276281696</v>
+        <v>0.6229069528303365</v>
       </c>
       <c r="T88">
-        <v>5.182417784656846</v>
+        <v>5.581065306553526</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06504140811661721</v>
+        <v>0.06429380572447219</v>
       </c>
       <c r="W88">
-        <v>0.2204632359661017</v>
+        <v>0.2206395206101695</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2601656324664688</v>
+        <v>0.2571752228978887</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8668,22 +8668,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2729342867987912</v>
+        <v>0.2748342867987912</v>
       </c>
       <c r="C89">
-        <v>-11.21104064800656</v>
+        <v>-11.52462250392972</v>
       </c>
       <c r="D89">
-        <v>7.800649351993441</v>
+        <v>7.735937496070278</v>
       </c>
       <c r="E89">
-        <v>21.26469</v>
+        <v>21.51356</v>
       </c>
       <c r="F89">
-        <v>21.65169</v>
+        <v>21.90056</v>
       </c>
       <c r="G89">
         <v>2.64</v>
@@ -8704,37 +8704,37 @@
         <v>1.313</v>
       </c>
       <c r="M89">
-        <v>5.105468502</v>
+        <v>5.164152048000001</v>
       </c>
       <c r="N89">
-        <v>-3.792468502</v>
+        <v>-3.851152048000001</v>
       </c>
       <c r="O89">
-        <v>-0.9481171254999999</v>
+        <v>-0.9627880120000002</v>
       </c>
       <c r="P89">
-        <v>-2.8443513765</v>
+        <v>-2.888364036</v>
       </c>
       <c r="Q89">
-        <v>-2.5873513765</v>
+        <v>-2.631364036</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6229069528303365</v>
+        <v>0.6709991988995313</v>
       </c>
       <c r="T89">
-        <v>5.581065306553526</v>
+        <v>6.046154082099655</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06429380572447219</v>
+        <v>0.063563194295785</v>
       </c>
       <c r="W89">
-        <v>0.2206395206101695</v>
+        <v>0.2208117987850539</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2571752228978887</v>
+        <v>0.25425277718314</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8750,22 +8750,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2748342867987912</v>
+        <v>0.2767342867987912</v>
       </c>
       <c r="C90">
-        <v>-11.52462250392972</v>
+        <v>-11.83713953290182</v>
       </c>
       <c r="D90">
-        <v>7.735937496070278</v>
+        <v>7.672290467098181</v>
       </c>
       <c r="E90">
-        <v>21.51356</v>
+        <v>21.76243</v>
       </c>
       <c r="F90">
-        <v>21.90056</v>
+        <v>22.14943</v>
       </c>
       <c r="G90">
         <v>2.64</v>
@@ -8786,37 +8786,37 @@
         <v>1.313</v>
       </c>
       <c r="M90">
-        <v>5.164152048000001</v>
+        <v>5.222835594000001</v>
       </c>
       <c r="N90">
-        <v>-3.851152048000001</v>
+        <v>-3.909835594000001</v>
       </c>
       <c r="O90">
-        <v>-0.9627880120000002</v>
+        <v>-0.9774588985000002</v>
       </c>
       <c r="P90">
-        <v>-2.888364036</v>
+        <v>-2.932376695500001</v>
       </c>
       <c r="Q90">
-        <v>-2.631364036</v>
+        <v>-2.675376695500001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6709991988995313</v>
+        <v>0.7278354897085797</v>
       </c>
       <c r="T90">
-        <v>6.046154082099655</v>
+        <v>6.595804453199625</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.063563194295785</v>
+        <v>0.06284900110145032</v>
       </c>
       <c r="W90">
-        <v>0.2208117987850539</v>
+        <v>0.220980205540278</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.25425277718314</v>
+        <v>0.2513960044058013</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8832,22 +8832,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2767342867987912</v>
+        <v>0.2786342867987912</v>
       </c>
       <c r="C91">
-        <v>-11.83713953290182</v>
+        <v>-12.14861780287747</v>
       </c>
       <c r="D91">
-        <v>7.672290467098181</v>
+        <v>7.609682197122529</v>
       </c>
       <c r="E91">
-        <v>21.76243</v>
+        <v>22.0113</v>
       </c>
       <c r="F91">
-        <v>22.14943</v>
+        <v>22.3983</v>
       </c>
       <c r="G91">
         <v>2.64</v>
@@ -8868,37 +8868,37 @@
         <v>1.313</v>
       </c>
       <c r="M91">
-        <v>5.222835594000001</v>
+        <v>5.281519140000001</v>
       </c>
       <c r="N91">
-        <v>-3.909835594000001</v>
+        <v>-3.968519140000001</v>
       </c>
       <c r="O91">
-        <v>-0.9774588985000002</v>
+        <v>-0.9921297850000003</v>
       </c>
       <c r="P91">
-        <v>-2.932376695500001</v>
+        <v>-2.976389355000001</v>
       </c>
       <c r="Q91">
-        <v>-2.675376695500001</v>
+        <v>-2.719389355000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7278354897085797</v>
+        <v>0.7960390386794377</v>
       </c>
       <c r="T91">
-        <v>6.595804453199625</v>
+        <v>7.255384898519587</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06284900110145032</v>
+        <v>0.06215067886698977</v>
       </c>
       <c r="W91">
-        <v>0.220980205540278</v>
+        <v>0.2211448699231638</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2513960044058013</v>
+        <v>0.2486027154679591</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8914,22 +8914,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2786342867987912</v>
+        <v>0.2805342867987912</v>
       </c>
       <c r="C92">
-        <v>-12.14861780287747</v>
+        <v>-12.45908253780823</v>
       </c>
       <c r="D92">
-        <v>7.609682197122529</v>
+        <v>7.548087462191768</v>
       </c>
       <c r="E92">
-        <v>22.0113</v>
+        <v>22.26017</v>
       </c>
       <c r="F92">
-        <v>22.3983</v>
+        <v>22.64717</v>
       </c>
       <c r="G92">
         <v>2.64</v>
@@ -8950,37 +8950,37 @@
         <v>1.313</v>
       </c>
       <c r="M92">
-        <v>5.281519140000001</v>
+        <v>5.340202686</v>
       </c>
       <c r="N92">
-        <v>-3.968519140000001</v>
+        <v>-4.027202686000001</v>
       </c>
       <c r="O92">
-        <v>-0.9921297850000003</v>
+        <v>-1.0068006715</v>
       </c>
       <c r="P92">
-        <v>-2.976389355000001</v>
+        <v>-3.020402014500001</v>
       </c>
       <c r="Q92">
-        <v>-2.719389355000001</v>
+        <v>-2.7634020145</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7960390386794377</v>
+        <v>0.879398931866042</v>
       </c>
       <c r="T92">
-        <v>7.255384898519587</v>
+        <v>8.061538776132876</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06215067886698977</v>
+        <v>0.06146770437394593</v>
       </c>
       <c r="W92">
-        <v>0.2211448699231638</v>
+        <v>0.2213059153086236</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2486027154679591</v>
+        <v>0.2458708174957837</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8996,22 +8996,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2805342867987912</v>
+        <v>0.2824342867987912</v>
       </c>
       <c r="C93">
-        <v>-12.45908253780823</v>
+        <v>-12.76855815152624</v>
       </c>
       <c r="D93">
-        <v>7.548087462191768</v>
+        <v>7.487481848473759</v>
       </c>
       <c r="E93">
-        <v>22.26017</v>
+        <v>22.50904</v>
       </c>
       <c r="F93">
-        <v>22.64717</v>
+        <v>22.89604</v>
       </c>
       <c r="G93">
         <v>2.64</v>
@@ -9032,37 +9032,37 @@
         <v>1.313</v>
       </c>
       <c r="M93">
-        <v>5.340202686</v>
+        <v>5.398886232000001</v>
       </c>
       <c r="N93">
-        <v>-4.027202686000001</v>
+        <v>-4.085886232</v>
       </c>
       <c r="O93">
-        <v>-1.0068006715</v>
+        <v>-1.021471558</v>
       </c>
       <c r="P93">
-        <v>-3.020402014500001</v>
+        <v>-3.064414674</v>
       </c>
       <c r="Q93">
-        <v>-2.7634020145</v>
+        <v>-2.807414674</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.879398931866042</v>
+        <v>0.9835987983492975</v>
       </c>
       <c r="T93">
-        <v>8.061538776132876</v>
+        <v>9.069231123149487</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06146770437394593</v>
+        <v>0.06079957715248999</v>
       </c>
       <c r="W93">
-        <v>0.2213059153086236</v>
+        <v>0.2214634597074429</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2458708174957837</v>
+        <v>0.2431983086099601</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9078,22 +9078,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2824342867987912</v>
+        <v>0.2843342867987912</v>
       </c>
       <c r="C94">
-        <v>-12.76855815152624</v>
+        <v>-13.07706828000849</v>
       </c>
       <c r="D94">
-        <v>7.487481848473759</v>
+        <v>7.427841719991515</v>
       </c>
       <c r="E94">
-        <v>22.50904</v>
+        <v>22.75791</v>
       </c>
       <c r="F94">
-        <v>22.89604</v>
+        <v>23.14491</v>
       </c>
       <c r="G94">
         <v>2.64</v>
@@ -9114,37 +9114,37 @@
         <v>1.313</v>
       </c>
       <c r="M94">
-        <v>5.398886232000001</v>
+        <v>5.457569778000001</v>
       </c>
       <c r="N94">
-        <v>-4.085886232</v>
+        <v>-4.144569778000001</v>
       </c>
       <c r="O94">
-        <v>-1.021471558</v>
+        <v>-1.0361424445</v>
       </c>
       <c r="P94">
-        <v>-3.064414674</v>
+        <v>-3.108427333500001</v>
       </c>
       <c r="Q94">
-        <v>-2.807414674</v>
+        <v>-2.851427333500001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9835987983492975</v>
+        <v>1.11757005525634</v>
       </c>
       <c r="T94">
-        <v>9.069231123149487</v>
+        <v>10.3648355693137</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06079957715248999</v>
+        <v>0.0601458182583772</v>
       </c>
       <c r="W94">
-        <v>0.2214634597074429</v>
+        <v>0.2216176160546747</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2431983086099601</v>
+        <v>0.2405832730335087</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9160,22 +9160,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2843342867987912</v>
+        <v>0.2862342867987913</v>
       </c>
       <c r="C95">
-        <v>-13.07706828000849</v>
+        <v>-13.38463581211128</v>
       </c>
       <c r="D95">
-        <v>7.427841719991515</v>
+        <v>7.369144187888722</v>
       </c>
       <c r="E95">
-        <v>22.75791</v>
+        <v>23.00678</v>
       </c>
       <c r="F95">
-        <v>23.14491</v>
+        <v>23.39378</v>
       </c>
       <c r="G95">
         <v>2.64</v>
@@ -9196,37 +9196,37 @@
         <v>1.313</v>
       </c>
       <c r="M95">
-        <v>5.457569778000001</v>
+        <v>5.516253324000001</v>
       </c>
       <c r="N95">
-        <v>-4.144569778000001</v>
+        <v>-4.203253324</v>
       </c>
       <c r="O95">
-        <v>-1.0361424445</v>
+        <v>-1.050813331</v>
       </c>
       <c r="P95">
-        <v>-3.108427333500001</v>
+        <v>-3.152439993</v>
       </c>
       <c r="Q95">
-        <v>-2.851427333500001</v>
+        <v>-2.895439993</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.11757005525634</v>
+        <v>1.296198397799064</v>
       </c>
       <c r="T95">
-        <v>10.3648355693137</v>
+        <v>12.09230816419932</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0601458182583772</v>
+        <v>0.05950596912796893</v>
       </c>
       <c r="W95">
-        <v>0.2216176160546747</v>
+        <v>0.2217684924796249</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2405832730335087</v>
+        <v>0.2380238765118758</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9242,22 +9242,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2862342867987913</v>
+        <v>0.2881342867987912</v>
       </c>
       <c r="C96">
-        <v>-13.38463581211128</v>
+        <v>-13.69128291885893</v>
       </c>
       <c r="D96">
-        <v>7.369144187888722</v>
+        <v>7.311367081141078</v>
       </c>
       <c r="E96">
-        <v>23.00678</v>
+        <v>23.25565</v>
       </c>
       <c r="F96">
-        <v>23.39378</v>
+        <v>23.64265</v>
       </c>
       <c r="G96">
         <v>2.64</v>
@@ -9278,37 +9278,37 @@
         <v>1.313</v>
       </c>
       <c r="M96">
-        <v>5.516253324000001</v>
+        <v>5.574936870000001</v>
       </c>
       <c r="N96">
-        <v>-4.203253324</v>
+        <v>-4.261936870000001</v>
       </c>
       <c r="O96">
-        <v>-1.050813331</v>
+        <v>-1.0654842175</v>
       </c>
       <c r="P96">
-        <v>-3.152439993</v>
+        <v>-3.196452652500001</v>
       </c>
       <c r="Q96">
-        <v>-2.895439993</v>
+        <v>-2.939452652500001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.296198397799064</v>
+        <v>1.546278077358877</v>
       </c>
       <c r="T96">
-        <v>12.09230816419932</v>
+        <v>14.51076979703919</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05950596912796893</v>
+        <v>0.05887959050556926</v>
       </c>
       <c r="W96">
-        <v>0.2217684924796249</v>
+        <v>0.2219161925587868</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2380238765118758</v>
+        <v>0.2355183620222769</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9324,22 +9324,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2881342867987912</v>
+        <v>0.2900342867987912</v>
       </c>
       <c r="C97">
-        <v>-13.69128291885893</v>
+        <v>-13.99703108136529</v>
       </c>
       <c r="D97">
-        <v>7.311367081141078</v>
+        <v>7.254488918634711</v>
       </c>
       <c r="E97">
-        <v>23.25565</v>
+        <v>23.50452</v>
       </c>
       <c r="F97">
-        <v>23.64265</v>
+        <v>23.89152</v>
       </c>
       <c r="G97">
         <v>2.64</v>
@@ -9360,37 +9360,37 @@
         <v>1.313</v>
       </c>
       <c r="M97">
-        <v>5.574936870000001</v>
+        <v>5.633620416000001</v>
       </c>
       <c r="N97">
-        <v>-4.261936870000001</v>
+        <v>-4.320620416000001</v>
       </c>
       <c r="O97">
-        <v>-1.0654842175</v>
+        <v>-1.080155104</v>
       </c>
       <c r="P97">
-        <v>-3.196452652500001</v>
+        <v>-3.240465312</v>
       </c>
       <c r="Q97">
-        <v>-2.939452652500001</v>
+        <v>-2.983465312</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.546278077358877</v>
+        <v>1.921397596698598</v>
       </c>
       <c r="T97">
-        <v>14.51076979703919</v>
+        <v>18.138462246299</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05887959050556926</v>
+        <v>0.0582662614378029</v>
       </c>
       <c r="W97">
-        <v>0.2219161925587868</v>
+        <v>0.2220608155529661</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2355183620222769</v>
+        <v>0.2330650457512117</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9406,22 +9406,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2900342867987912</v>
+        <v>0.2919342867987912</v>
       </c>
       <c r="C98">
-        <v>-13.99703108136529</v>
+        <v>-14.30190111746214</v>
       </c>
       <c r="D98">
-        <v>7.254488918634713</v>
+        <v>7.198488882537856</v>
       </c>
       <c r="E98">
-        <v>23.50452</v>
+        <v>23.75339</v>
       </c>
       <c r="F98">
-        <v>23.89152</v>
+        <v>24.14039</v>
       </c>
       <c r="G98">
         <v>2.64</v>
@@ -9442,37 +9442,37 @@
         <v>1.313</v>
       </c>
       <c r="M98">
-        <v>5.633620416</v>
+        <v>5.692303962</v>
       </c>
       <c r="N98">
-        <v>-4.320620416000001</v>
+        <v>-4.379303962</v>
       </c>
       <c r="O98">
-        <v>-1.080155104</v>
+        <v>-1.0948259905</v>
       </c>
       <c r="P98">
-        <v>-3.240465312</v>
+        <v>-3.2844779715</v>
       </c>
       <c r="Q98">
-        <v>-2.983465312</v>
+        <v>-3.0274779715</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.921397596698593</v>
+        <v>2.546596795598123</v>
       </c>
       <c r="T98">
-        <v>18.13846224629895</v>
+        <v>24.1846163283986</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05826626143780292</v>
+        <v>0.0576655783301967</v>
       </c>
       <c r="W98">
-        <v>0.2220608155529661</v>
+        <v>0.2222024566297396</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2330650457512116</v>
+        <v>0.2306623133207869</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9488,22 +9488,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2919342867987912</v>
+        <v>0.2938342867987912</v>
       </c>
       <c r="C99">
-        <v>-14.30190111746214</v>
+        <v>-14.60591320710363</v>
       </c>
       <c r="D99">
-        <v>7.198488882537856</v>
+        <v>7.143346792896367</v>
       </c>
       <c r="E99">
-        <v>23.75339</v>
+        <v>24.00226</v>
       </c>
       <c r="F99">
-        <v>24.14039</v>
+        <v>24.38926</v>
       </c>
       <c r="G99">
         <v>2.64</v>
@@ -9524,37 +9524,37 @@
         <v>1.313</v>
       </c>
       <c r="M99">
-        <v>5.692303962</v>
+        <v>5.750987508000001</v>
       </c>
       <c r="N99">
-        <v>-4.379303962</v>
+        <v>-4.437987508000001</v>
       </c>
       <c r="O99">
-        <v>-1.0948259905</v>
+        <v>-1.109496877</v>
       </c>
       <c r="P99">
-        <v>-3.2844779715</v>
+        <v>-3.328490631000001</v>
       </c>
       <c r="Q99">
-        <v>-3.0274779715</v>
+        <v>-3.071490631000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.546596795598123</v>
+        <v>3.796995193397184</v>
       </c>
       <c r="T99">
-        <v>24.1846163283986</v>
+        <v>36.27692449259789</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0576655783301967</v>
+        <v>0.05707715406152122</v>
       </c>
       <c r="W99">
-        <v>0.2222024566297396</v>
+        <v>0.2223412070722933</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2306623133207869</v>
+        <v>0.2283086162460848</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9570,22 +9570,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2938342867987912</v>
+        <v>0.2957342867987912</v>
       </c>
       <c r="C100">
-        <v>-14.60591320710363</v>
+        <v>-14.909086916612</v>
       </c>
       <c r="D100">
-        <v>7.143346792896367</v>
+        <v>7.089043083387997</v>
       </c>
       <c r="E100">
-        <v>24.00226</v>
+        <v>24.25113</v>
       </c>
       <c r="F100">
-        <v>24.38926</v>
+        <v>24.63813</v>
       </c>
       <c r="G100">
         <v>2.64</v>
@@ -9606,37 +9606,37 @@
         <v>1.313</v>
       </c>
       <c r="M100">
-        <v>5.750987508000001</v>
+        <v>5.809671054000001</v>
       </c>
       <c r="N100">
-        <v>-4.437987508000001</v>
+        <v>-4.496671054</v>
       </c>
       <c r="O100">
-        <v>-1.109496877</v>
+        <v>-1.1241677635</v>
       </c>
       <c r="P100">
-        <v>-3.328490631000001</v>
+        <v>-3.3725032905</v>
       </c>
       <c r="Q100">
-        <v>-3.071490631000001</v>
+        <v>-3.1155032905</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.796995193397184</v>
+        <v>7.54819038679437</v>
       </c>
       <c r="T100">
-        <v>36.27692449259789</v>
+        <v>72.5538489851958</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05707715406152122</v>
+        <v>0.05650061715180889</v>
       </c>
       <c r="W100">
-        <v>0.2223412070722933</v>
+        <v>0.2224771544756035</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9644,91 +9644,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2283086162460848</v>
+        <v>0.2260024686072356</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2957342867987912</v>
-      </c>
-      <c r="C101">
-        <v>-14.909086916612</v>
-      </c>
-      <c r="D101">
-        <v>7.089043083387997</v>
-      </c>
-      <c r="E101">
-        <v>24.25113</v>
-      </c>
-      <c r="F101">
-        <v>24.63813</v>
-      </c>
-      <c r="G101">
-        <v>2.64</v>
-      </c>
-      <c r="H101">
-        <v>24.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.57</v>
-      </c>
-      <c r="K101">
-        <v>0.257</v>
-      </c>
-      <c r="L101">
-        <v>1.313</v>
-      </c>
-      <c r="M101">
-        <v>5.809671054000001</v>
-      </c>
-      <c r="N101">
-        <v>-4.496671054</v>
-      </c>
-      <c r="O101">
-        <v>-1.1241677635</v>
-      </c>
-      <c r="P101">
-        <v>-3.3725032905</v>
-      </c>
-      <c r="Q101">
-        <v>-3.1155032905</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.54819038679437</v>
-      </c>
-      <c r="T101">
-        <v>72.5538489851958</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05650061715180889</v>
-      </c>
-      <c r="W101">
-        <v>0.2224771544756035</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2260024686072356</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
